--- a/research/traditional_assets/database/data/czech_republic/czech_republic_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_beverage_soft.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07946791842877482</v>
+        <v>0.07935337938376015</v>
       </c>
       <c r="C2">
-        <v>559.782063681753</v>
+        <v>555.0504665835343</v>
       </c>
       <c r="D2">
-        <v>559.782063681753</v>
+        <v>560.6654665835343</v>
       </c>
       <c r="E2">
-        <v>-219</v>
+        <v>-213.385</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.615</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1439,28 +1439,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2824345</v>
       </c>
       <c r="N2">
-        <v>65.47499999999999</v>
+        <v>65.1925655</v>
       </c>
       <c r="O2">
-        <v>12.44025</v>
+        <v>12.386587445</v>
       </c>
       <c r="P2">
-        <v>53.03475</v>
+        <v>52.805978055</v>
       </c>
       <c r="Q2">
-        <v>65.43474999999999</v>
+        <v>65.205978055</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07946791842877482</v>
+        <v>0.07974338321591934</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6616197176642237</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>231.823661769366</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07935337938376015</v>
+        <v>0.07923884033874547</v>
       </c>
       <c r="C3">
-        <v>555.0504665835343</v>
+        <v>550.3216621228424</v>
       </c>
       <c r="D3">
-        <v>560.6654665835343</v>
+        <v>561.5516621228425</v>
       </c>
       <c r="E3">
-        <v>-213.385</v>
+        <v>-207.77</v>
       </c>
       <c r="F3">
-        <v>5.615</v>
+        <v>11.23</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1521,28 +1521,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M3">
-        <v>0.2824345</v>
+        <v>0.564869</v>
       </c>
       <c r="N3">
-        <v>65.1925655</v>
+        <v>64.91013099999999</v>
       </c>
       <c r="O3">
-        <v>12.386587445</v>
+        <v>12.33292489</v>
       </c>
       <c r="P3">
-        <v>52.805978055</v>
+        <v>52.57720610999999</v>
       </c>
       <c r="Q3">
-        <v>65.205978055</v>
+        <v>64.97720611</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07974338321591934</v>
+        <v>0.08002446973341375</v>
       </c>
       <c r="T3">
-        <v>0.6616197176642237</v>
+        <v>0.6670986170762496</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>231.823661769366</v>
+        <v>115.911830884683</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07923884033874547</v>
+        <v>0.0791243012937308</v>
       </c>
       <c r="C4">
-        <v>550.3216621228424</v>
+        <v>545.5956635628851</v>
       </c>
       <c r="D4">
-        <v>561.5516621228425</v>
+        <v>562.4406635628851</v>
       </c>
       <c r="E4">
-        <v>-207.77</v>
+        <v>-202.155</v>
       </c>
       <c r="F4">
-        <v>11.23</v>
+        <v>16.845</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1603,28 +1603,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M4">
-        <v>0.564869</v>
+        <v>0.8473034999999999</v>
       </c>
       <c r="N4">
-        <v>64.91013099999999</v>
+        <v>64.6276965</v>
       </c>
       <c r="O4">
-        <v>12.33292489</v>
+        <v>12.279262335</v>
       </c>
       <c r="P4">
-        <v>52.57720610999999</v>
+        <v>52.348434165</v>
       </c>
       <c r="Q4">
-        <v>64.97720611</v>
+        <v>64.74843416499999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08002446973341375</v>
+        <v>0.08031135184920701</v>
       </c>
       <c r="T4">
-        <v>0.6670986170762496</v>
+        <v>0.6726904834864617</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>115.911830884683</v>
+        <v>77.27455392312201</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0791243012937308</v>
+        <v>0.07900976224871613</v>
       </c>
       <c r="C5">
-        <v>545.5956635628851</v>
+        <v>540.8724842509918</v>
       </c>
       <c r="D5">
-        <v>562.4406635628851</v>
+        <v>563.3324842509918</v>
       </c>
       <c r="E5">
-        <v>-202.155</v>
+        <v>-196.54</v>
       </c>
       <c r="F5">
-        <v>16.845</v>
+        <v>22.46</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1685,28 +1685,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M5">
-        <v>0.8473034999999999</v>
+        <v>1.129738</v>
       </c>
       <c r="N5">
-        <v>64.6276965</v>
+        <v>64.34526199999999</v>
       </c>
       <c r="O5">
-        <v>12.279262335</v>
+        <v>12.22559978</v>
       </c>
       <c r="P5">
-        <v>52.348434165</v>
+        <v>52.11966222</v>
       </c>
       <c r="Q5">
-        <v>64.74843416499999</v>
+        <v>64.51966221999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08031135184920701</v>
+        <v>0.08060421067574597</v>
       </c>
       <c r="T5">
-        <v>0.6726904834864617</v>
+        <v>0.678398847113553</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>77.27455392312201</v>
+        <v>57.95591544234149</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07900976224871613</v>
+        <v>0.07889522320370145</v>
       </c>
       <c r="C6">
-        <v>540.8724842509918</v>
+        <v>536.1521376192826</v>
       </c>
       <c r="D6">
-        <v>563.3324842509918</v>
+        <v>564.2271376192826</v>
       </c>
       <c r="E6">
-        <v>-196.54</v>
+        <v>-190.925</v>
       </c>
       <c r="F6">
-        <v>22.46</v>
+        <v>28.075</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1767,28 +1767,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M6">
-        <v>1.129738</v>
+        <v>1.4121725</v>
       </c>
       <c r="N6">
-        <v>64.34526199999999</v>
+        <v>64.0628275</v>
       </c>
       <c r="O6">
-        <v>12.22559978</v>
+        <v>12.171937225</v>
       </c>
       <c r="P6">
-        <v>52.11966222</v>
+        <v>51.890890275</v>
       </c>
       <c r="Q6">
-        <v>64.51966221999999</v>
+        <v>64.290890275</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08060421067574597</v>
+        <v>0.08090323495126468</v>
       </c>
       <c r="T6">
-        <v>0.678398847113553</v>
+        <v>0.6842273868170042</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.95591544234149</v>
+        <v>46.36473235387319</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07889522320370145</v>
+        <v>0.07878068415868678</v>
       </c>
       <c r="C7">
-        <v>536.1521376192826</v>
+        <v>531.434637185341</v>
       </c>
       <c r="D7">
-        <v>564.2271376192826</v>
+        <v>565.124637185341</v>
       </c>
       <c r="E7">
-        <v>-190.925</v>
+        <v>-185.31</v>
       </c>
       <c r="F7">
-        <v>28.075</v>
+        <v>33.69</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1849,28 +1849,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M7">
-        <v>1.4121725</v>
+        <v>1.694607</v>
       </c>
       <c r="N7">
-        <v>64.0628275</v>
+        <v>63.780393</v>
       </c>
       <c r="O7">
-        <v>12.171937225</v>
+        <v>12.11827467</v>
       </c>
       <c r="P7">
-        <v>51.890890275</v>
+        <v>51.66211833</v>
       </c>
       <c r="Q7">
-        <v>64.290890275</v>
+        <v>64.06211833</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08090323495126468</v>
+        <v>0.08120862144541147</v>
       </c>
       <c r="T7">
-        <v>0.6842273868170042</v>
+        <v>0.6901799380035076</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.36473235387319</v>
+        <v>38.63727696156099</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07878068415868678</v>
+        <v>0.07866614511367212</v>
       </c>
       <c r="C8">
-        <v>531.434637185341</v>
+        <v>526.7199965528963</v>
       </c>
       <c r="D8">
-        <v>565.124637185341</v>
+        <v>566.0249965528963</v>
       </c>
       <c r="E8">
-        <v>-185.31</v>
+        <v>-179.695</v>
       </c>
       <c r="F8">
-        <v>33.69</v>
+        <v>39.30499999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1931,28 +1931,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M8">
-        <v>1.694607</v>
+        <v>1.977041499999999</v>
       </c>
       <c r="N8">
-        <v>63.780393</v>
+        <v>63.4979585</v>
       </c>
       <c r="O8">
-        <v>12.11827467</v>
+        <v>12.064612115</v>
       </c>
       <c r="P8">
-        <v>51.66211833</v>
+        <v>51.43334638499999</v>
       </c>
       <c r="Q8">
-        <v>64.06211833</v>
+        <v>63.83334638499999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08120862144541147</v>
+        <v>0.08152057539104528</v>
       </c>
       <c r="T8">
-        <v>0.6901799380035076</v>
+        <v>0.6962605010434844</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.637276961561</v>
+        <v>33.11766596705229</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07866614511367211</v>
+        <v>0.07855160606865744</v>
       </c>
       <c r="C9">
-        <v>526.7199965528964</v>
+        <v>522.0082294125102</v>
       </c>
       <c r="D9">
-        <v>566.0249965528964</v>
+        <v>566.9282294125102</v>
       </c>
       <c r="E9">
-        <v>-179.695</v>
+        <v>-174.08</v>
       </c>
       <c r="F9">
-        <v>39.30500000000001</v>
+        <v>44.92</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2013,28 +2013,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M9">
-        <v>1.9770415</v>
+        <v>2.259476</v>
       </c>
       <c r="N9">
-        <v>63.4979585</v>
+        <v>63.21552399999999</v>
       </c>
       <c r="O9">
-        <v>12.064612115</v>
+        <v>12.01094956</v>
       </c>
       <c r="P9">
-        <v>51.43334638499999</v>
+        <v>51.20457443999999</v>
       </c>
       <c r="Q9">
-        <v>63.83334638499999</v>
+        <v>63.60457443999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08152057539104528</v>
+        <v>0.08183931094419286</v>
       </c>
       <c r="T9">
-        <v>0.6962605010434844</v>
+        <v>0.702473250236504</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.11766596705228</v>
+        <v>28.97795772117075</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07855160606865744</v>
+        <v>0.07843706702364277</v>
       </c>
       <c r="C10">
-        <v>522.0082294125102</v>
+        <v>517.2993495422703</v>
       </c>
       <c r="D10">
-        <v>566.9282294125102</v>
+        <v>567.8343495422703</v>
       </c>
       <c r="E10">
-        <v>-174.08</v>
+        <v>-168.465</v>
       </c>
       <c r="F10">
-        <v>44.92</v>
+        <v>50.535</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2095,28 +2095,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M10">
-        <v>2.259476</v>
+        <v>2.5419105</v>
       </c>
       <c r="N10">
-        <v>63.21552399999999</v>
+        <v>62.93308949999999</v>
       </c>
       <c r="O10">
-        <v>12.01094956</v>
+        <v>11.957287005</v>
       </c>
       <c r="P10">
-        <v>51.20457443999999</v>
+        <v>50.975802495</v>
       </c>
       <c r="Q10">
-        <v>63.60457443999999</v>
+        <v>63.37580249499999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08183931094419286</v>
+        <v>0.0821650516743327</v>
       </c>
       <c r="T10">
-        <v>0.702473250236504</v>
+        <v>0.7088225433678316</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.97795772117075</v>
+        <v>25.75818464104067</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07843706702364277</v>
+        <v>0.07832252797862811</v>
       </c>
       <c r="C11">
-        <v>517.2993495422703</v>
+        <v>512.5933708084915</v>
       </c>
       <c r="D11">
-        <v>567.8343495422703</v>
+        <v>568.7433708084915</v>
       </c>
       <c r="E11">
-        <v>-168.465</v>
+        <v>-162.85</v>
       </c>
       <c r="F11">
-        <v>50.535</v>
+        <v>56.15</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2177,28 +2177,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M11">
-        <v>2.5419105</v>
+        <v>2.824345</v>
       </c>
       <c r="N11">
-        <v>62.93308949999999</v>
+        <v>62.65065499999999</v>
       </c>
       <c r="O11">
-        <v>11.957287005</v>
+        <v>11.90362445</v>
       </c>
       <c r="P11">
-        <v>50.975802495</v>
+        <v>50.74703054999999</v>
       </c>
       <c r="Q11">
-        <v>63.37580249499999</v>
+        <v>63.14703054999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0821650516743327</v>
+        <v>0.08249803108736456</v>
       </c>
       <c r="T11">
-        <v>0.7088225433678316</v>
+        <v>0.7153129319020778</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.75818464104067</v>
+        <v>23.1823661769366</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07832252797862811</v>
+        <v>0.07820798893361341</v>
       </c>
       <c r="C12">
-        <v>512.5933708084915</v>
+        <v>507.8903071664234</v>
       </c>
       <c r="D12">
-        <v>568.7433708084915</v>
+        <v>569.6553071664234</v>
       </c>
       <c r="E12">
-        <v>-162.85</v>
+        <v>-157.235</v>
       </c>
       <c r="F12">
-        <v>56.15000000000001</v>
+        <v>61.765</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2259,28 +2259,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M12">
-        <v>2.824345</v>
+        <v>3.1067795</v>
       </c>
       <c r="N12">
-        <v>62.65065499999999</v>
+        <v>62.36822049999999</v>
       </c>
       <c r="O12">
-        <v>11.90362445</v>
+        <v>11.849961895</v>
       </c>
       <c r="P12">
-        <v>50.74703054999999</v>
+        <v>50.51825860499999</v>
       </c>
       <c r="Q12">
-        <v>63.14703054999999</v>
+        <v>62.91825860499999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08249803108736456</v>
+        <v>0.08283849318383529</v>
       </c>
       <c r="T12">
-        <v>0.7153129319020778</v>
+        <v>0.7219491718640596</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.1823661769366</v>
+        <v>21.07487834266963</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07820798893361341</v>
+        <v>0.07809344988859875</v>
       </c>
       <c r="C13">
-        <v>507.8903071664234</v>
+        <v>503.1901726609634</v>
       </c>
       <c r="D13">
-        <v>569.6553071664234</v>
+        <v>570.5701726609634</v>
       </c>
       <c r="E13">
-        <v>-157.235</v>
+        <v>-151.62</v>
       </c>
       <c r="F13">
-        <v>61.765</v>
+        <v>67.38</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2341,28 +2341,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M13">
-        <v>3.1067795</v>
+        <v>3.389214</v>
       </c>
       <c r="N13">
-        <v>62.36822049999999</v>
+        <v>62.08578599999999</v>
       </c>
       <c r="O13">
-        <v>11.849961895</v>
+        <v>11.79629934</v>
       </c>
       <c r="P13">
-        <v>50.51825860499999</v>
+        <v>50.28948665999999</v>
       </c>
       <c r="Q13">
-        <v>62.91825860499999</v>
+        <v>62.68948665999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08283849318383529</v>
+        <v>0.08318669305522584</v>
       </c>
       <c r="T13">
-        <v>0.7219491718640596</v>
+        <v>0.7287362354615411</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.07487834266963</v>
+        <v>19.3186384807805</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07809344988859875</v>
+        <v>0.07797891084358409</v>
       </c>
       <c r="C14">
-        <v>503.1901726609634</v>
+        <v>498.4929814273781</v>
       </c>
       <c r="D14">
-        <v>570.5701726609634</v>
+        <v>571.4879814273781</v>
       </c>
       <c r="E14">
-        <v>-151.62</v>
+        <v>-146.005</v>
       </c>
       <c r="F14">
-        <v>67.38</v>
+        <v>72.995</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2423,28 +2423,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M14">
-        <v>3.389214</v>
+        <v>3.6716485</v>
       </c>
       <c r="N14">
-        <v>62.08578599999999</v>
+        <v>61.80335149999999</v>
       </c>
       <c r="O14">
-        <v>11.79629934</v>
+        <v>11.742636785</v>
       </c>
       <c r="P14">
-        <v>50.28948665999999</v>
+        <v>50.06071471499999</v>
       </c>
       <c r="Q14">
-        <v>62.68948665999999</v>
+        <v>62.46071471499999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08318669305522584</v>
+        <v>0.08354289752136101</v>
       </c>
       <c r="T14">
-        <v>0.7287362354615411</v>
+        <v>0.7356793235095396</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.3186384807805</v>
+        <v>17.83258936687431</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07797891084358409</v>
+        <v>0.07786437179856942</v>
       </c>
       <c r="C15">
-        <v>498.4929814273781</v>
+        <v>493.7987476920326</v>
       </c>
       <c r="D15">
-        <v>571.4879814273781</v>
+        <v>572.4087476920326</v>
       </c>
       <c r="E15">
-        <v>-146.005</v>
+        <v>-140.39</v>
       </c>
       <c r="F15">
-        <v>72.995</v>
+        <v>78.61000000000001</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2505,28 +2505,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M15">
-        <v>3.6716485</v>
+        <v>3.954083000000001</v>
       </c>
       <c r="N15">
-        <v>61.80335149999999</v>
+        <v>61.520917</v>
       </c>
       <c r="O15">
-        <v>11.742636785</v>
+        <v>11.68897423</v>
       </c>
       <c r="P15">
-        <v>50.06071471499999</v>
+        <v>49.83194277</v>
       </c>
       <c r="Q15">
-        <v>62.46071471499999</v>
+        <v>62.23194277</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08354289752136101</v>
+        <v>0.08390738581229001</v>
       </c>
       <c r="T15">
-        <v>0.7356793235095396</v>
+        <v>0.7427838787214449</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.83258936687431</v>
+        <v>16.55883298352614</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07786437179856942</v>
+        <v>0.07774983275355474</v>
       </c>
       <c r="C16">
-        <v>493.7987476920326</v>
+        <v>489.1074857731239</v>
       </c>
       <c r="D16">
-        <v>572.4087476920326</v>
+        <v>573.3324857731239</v>
       </c>
       <c r="E16">
-        <v>-140.39</v>
+        <v>-134.775</v>
       </c>
       <c r="F16">
-        <v>78.61000000000001</v>
+        <v>84.22500000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2587,28 +2587,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M16">
-        <v>3.954083000000001</v>
+        <v>4.236517500000001</v>
       </c>
       <c r="N16">
-        <v>61.520917</v>
+        <v>61.2384825</v>
       </c>
       <c r="O16">
-        <v>11.68897423</v>
+        <v>11.635311675</v>
       </c>
       <c r="P16">
-        <v>49.83194277</v>
+        <v>49.603170825</v>
       </c>
       <c r="Q16">
-        <v>62.23194277</v>
+        <v>62.003170825</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08390738581229001</v>
+        <v>0.08428045029829968</v>
       </c>
       <c r="T16">
-        <v>0.7427838787214449</v>
+        <v>0.7500555999383363</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.55883298352614</v>
+        <v>15.4549107846244</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07774983275355474</v>
+        <v>0.07763529370854007</v>
       </c>
       <c r="C17">
-        <v>489.1074857731239</v>
+        <v>484.4192100814236</v>
       </c>
       <c r="D17">
-        <v>573.3324857731239</v>
+        <v>574.2592100814236</v>
       </c>
       <c r="E17">
-        <v>-134.775</v>
+        <v>-129.16</v>
       </c>
       <c r="F17">
-        <v>84.22499999999999</v>
+        <v>89.84</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2669,28 +2669,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M17">
-        <v>4.2365175</v>
+        <v>4.518952</v>
       </c>
       <c r="N17">
-        <v>61.2384825</v>
+        <v>60.956048</v>
       </c>
       <c r="O17">
-        <v>11.635311675</v>
+        <v>11.58164912</v>
       </c>
       <c r="P17">
-        <v>49.603170825</v>
+        <v>49.37439887999999</v>
       </c>
       <c r="Q17">
-        <v>62.003170825</v>
+        <v>61.77439887999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08428045029829968</v>
+        <v>0.0846623972720715</v>
       </c>
       <c r="T17">
-        <v>0.7500555999383363</v>
+        <v>0.7575004573746773</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.4549107846244</v>
+        <v>14.48897886058537</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07763529370854007</v>
+        <v>0.07752075466352538</v>
       </c>
       <c r="C18">
-        <v>484.4192100814236</v>
+        <v>479.7339351210276</v>
       </c>
       <c r="D18">
-        <v>574.2592100814236</v>
+        <v>575.1889351210276</v>
       </c>
       <c r="E18">
-        <v>-129.16</v>
+        <v>-123.545</v>
       </c>
       <c r="F18">
-        <v>89.84</v>
+        <v>95.45500000000001</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2751,28 +2751,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M18">
-        <v>4.518952</v>
+        <v>4.8013865</v>
       </c>
       <c r="N18">
-        <v>60.956048</v>
+        <v>60.67361349999999</v>
       </c>
       <c r="O18">
-        <v>11.58164912</v>
+        <v>11.527986565</v>
       </c>
       <c r="P18">
-        <v>49.37439887999999</v>
+        <v>49.145626935</v>
       </c>
       <c r="Q18">
-        <v>61.77439887999999</v>
+        <v>61.54562693499999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0846623972720715</v>
+        <v>0.08505354778737997</v>
       </c>
       <c r="T18">
-        <v>0.7575004573746773</v>
+        <v>0.765124708966111</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.48897886058537</v>
+        <v>13.63668598643329</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07752075466352538</v>
+        <v>0.07740621561851072</v>
       </c>
       <c r="C19">
-        <v>479.7339351210276</v>
+        <v>475.0516754901126</v>
       </c>
       <c r="D19">
-        <v>575.1889351210276</v>
+        <v>576.1216754901126</v>
       </c>
       <c r="E19">
-        <v>-123.545</v>
+        <v>-117.93</v>
       </c>
       <c r="F19">
-        <v>95.45500000000001</v>
+        <v>101.07</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2833,28 +2833,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M19">
-        <v>4.8013865</v>
+        <v>5.083821</v>
       </c>
       <c r="N19">
-        <v>60.67361349999999</v>
+        <v>60.39117899999999</v>
       </c>
       <c r="O19">
-        <v>11.527986565</v>
+        <v>11.47432401</v>
       </c>
       <c r="P19">
-        <v>49.145626935</v>
+        <v>48.91685499</v>
       </c>
       <c r="Q19">
-        <v>61.54562693499999</v>
+        <v>61.31685499</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08505354778737997</v>
+        <v>0.0854542385591594</v>
       </c>
       <c r="T19">
-        <v>0.765124708966111</v>
+        <v>0.7729349179134332</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.63668598643329</v>
+        <v>12.87909232052033</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07740621561851072</v>
+        <v>0.07752252657349605</v>
       </c>
       <c r="C20">
-        <v>475.0516754901126</v>
+        <v>468.4895294232795</v>
       </c>
       <c r="D20">
-        <v>576.1216754901126</v>
+        <v>575.1745294232795</v>
       </c>
       <c r="E20">
-        <v>-117.93</v>
+        <v>-112.315</v>
       </c>
       <c r="F20">
-        <v>101.07</v>
+        <v>106.685</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2915,45 +2915,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M20">
-        <v>5.083820999999999</v>
+        <v>5.526283</v>
       </c>
       <c r="N20">
-        <v>60.39117899999999</v>
+        <v>59.94871699999999</v>
       </c>
       <c r="O20">
-        <v>11.47432401</v>
+        <v>11.39025623</v>
       </c>
       <c r="P20">
-        <v>48.91685499</v>
+        <v>48.55846077</v>
       </c>
       <c r="Q20">
-        <v>61.31685499</v>
+        <v>60.95846076999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0854542385591594</v>
+        <v>0.08586482293024203</v>
       </c>
       <c r="T20">
-        <v>0.7729349179134332</v>
+        <v>0.7809379715261214</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>12.87909232052033</v>
+        <v>11.84792744055996</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07752252657349605</v>
+        <v>0.07742013752848137</v>
       </c>
       <c r="C21">
-        <v>468.4895294232795</v>
+        <v>463.7081419614828</v>
       </c>
       <c r="D21">
-        <v>575.1745294232795</v>
+        <v>576.0081419614828</v>
       </c>
       <c r="E21">
-        <v>-112.315</v>
+        <v>-106.7</v>
       </c>
       <c r="F21">
-        <v>106.685</v>
+        <v>112.3</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2997,28 +2997,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M21">
-        <v>5.526283</v>
+        <v>5.81714</v>
       </c>
       <c r="N21">
-        <v>59.94871699999999</v>
+        <v>59.65785999999999</v>
       </c>
       <c r="O21">
-        <v>11.39025623</v>
+        <v>11.3349934</v>
       </c>
       <c r="P21">
-        <v>48.55846077</v>
+        <v>48.3228666</v>
       </c>
       <c r="Q21">
-        <v>60.95846076999999</v>
+        <v>60.7228666</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08586482293024203</v>
+        <v>0.08628567191060171</v>
       </c>
       <c r="T21">
-        <v>0.7809379715261214</v>
+        <v>0.7891411014791271</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.84792744055996</v>
+        <v>11.25553106853196</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07742013752848137</v>
+        <v>0.0773177484834667</v>
       </c>
       <c r="C22">
-        <v>463.7081419614828</v>
+        <v>458.9291743511835</v>
       </c>
       <c r="D22">
-        <v>576.0081419614828</v>
+        <v>576.8441743511835</v>
       </c>
       <c r="E22">
-        <v>-106.7</v>
+        <v>-101.085</v>
       </c>
       <c r="F22">
-        <v>112.3</v>
+        <v>117.915</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3079,28 +3079,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M22">
-        <v>5.81714</v>
+        <v>6.107997</v>
       </c>
       <c r="N22">
-        <v>59.65785999999999</v>
+        <v>59.367003</v>
       </c>
       <c r="O22">
-        <v>11.3349934</v>
+        <v>11.27973057</v>
       </c>
       <c r="P22">
-        <v>48.3228666</v>
+        <v>48.08727243</v>
       </c>
       <c r="Q22">
-        <v>60.7228666</v>
+        <v>60.48727243</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08628567191060171</v>
+        <v>0.08671717529552747</v>
       </c>
       <c r="T22">
-        <v>0.7891411014791271</v>
+        <v>0.7975519056081579</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.25553106853196</v>
+        <v>10.71955339860187</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0773177484834667</v>
+        <v>0.07721535943845204</v>
       </c>
       <c r="C23">
-        <v>458.9291743511835</v>
+        <v>454.1526371443929</v>
       </c>
       <c r="D23">
-        <v>576.8441743511835</v>
+        <v>577.6826371443929</v>
       </c>
       <c r="E23">
-        <v>-101.085</v>
+        <v>-95.47</v>
       </c>
       <c r="F23">
-        <v>117.915</v>
+        <v>123.53</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3161,28 +3161,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M23">
-        <v>6.107996999999999</v>
+        <v>6.398854</v>
       </c>
       <c r="N23">
-        <v>59.367003</v>
+        <v>59.07614599999999</v>
       </c>
       <c r="O23">
-        <v>11.27973057</v>
+        <v>11.22446774</v>
       </c>
       <c r="P23">
-        <v>48.08727243</v>
+        <v>47.85167825999999</v>
       </c>
       <c r="Q23">
-        <v>60.48727243</v>
+        <v>60.25167825999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08671717529552747</v>
+        <v>0.08715974286981029</v>
       </c>
       <c r="T23">
-        <v>0.7975519056081579</v>
+        <v>0.806178371381523</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.71955339860187</v>
+        <v>10.23230097139269</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07721535943845204</v>
+        <v>0.07742968039343737</v>
       </c>
       <c r="C24">
-        <v>454.1526371443929</v>
+        <v>446.7853455007098</v>
       </c>
       <c r="D24">
-        <v>577.6826371443929</v>
+        <v>575.9303455007098</v>
       </c>
       <c r="E24">
-        <v>-95.47</v>
+        <v>-89.85499999999999</v>
       </c>
       <c r="F24">
-        <v>123.53</v>
+        <v>129.145</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3243,45 +3243,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M24">
-        <v>6.398854</v>
+        <v>6.909257500000001</v>
       </c>
       <c r="N24">
-        <v>59.07614599999999</v>
+        <v>58.56574249999999</v>
       </c>
       <c r="O24">
-        <v>11.22446774</v>
+        <v>11.127491075</v>
       </c>
       <c r="P24">
-        <v>47.85167825999999</v>
+        <v>47.43825142499999</v>
       </c>
       <c r="Q24">
-        <v>60.25167825999999</v>
+        <v>59.83825142499999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08715974286981029</v>
+        <v>0.0876138057057628</v>
       </c>
       <c r="T24">
-        <v>0.806178371381523</v>
+        <v>0.8150289012009494</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.19</v>
       </c>
       <c r="W24">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.23230097139269</v>
+        <v>9.476416242989929</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07742968039343737</v>
+        <v>0.07734106134842268</v>
       </c>
       <c r="C25">
-        <v>446.7853455007098</v>
+        <v>441.8936056173485</v>
       </c>
       <c r="D25">
-        <v>575.9303455007098</v>
+        <v>576.6536056173485</v>
       </c>
       <c r="E25">
-        <v>-89.85499999999999</v>
+        <v>-84.23999999999998</v>
       </c>
       <c r="F25">
-        <v>129.145</v>
+        <v>134.76</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3325,28 +3325,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M25">
-        <v>6.909257500000001</v>
+        <v>7.209660000000001</v>
       </c>
       <c r="N25">
-        <v>58.56574249999999</v>
+        <v>58.26533999999999</v>
       </c>
       <c r="O25">
-        <v>11.127491075</v>
+        <v>11.0704146</v>
       </c>
       <c r="P25">
-        <v>47.43825142499999</v>
+        <v>47.1949254</v>
       </c>
       <c r="Q25">
-        <v>59.83825142499999</v>
+        <v>59.59492539999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0876138057057628</v>
+        <v>0.08807981756371405</v>
       </c>
       <c r="T25">
-        <v>0.8150289012009494</v>
+        <v>0.8241123396998346</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.476416242989929</v>
+        <v>9.081565566198682</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07734106134842268</v>
+        <v>0.07725244230340801</v>
       </c>
       <c r="C26">
-        <v>441.8936056173485</v>
+        <v>437.0036845752693</v>
       </c>
       <c r="D26">
-        <v>576.6536056173485</v>
+        <v>577.3786845752693</v>
       </c>
       <c r="E26">
-        <v>-84.24000000000001</v>
+        <v>-78.625</v>
       </c>
       <c r="F26">
-        <v>134.76</v>
+        <v>140.375</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3407,28 +3407,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M26">
-        <v>7.20966</v>
+        <v>7.5100625</v>
       </c>
       <c r="N26">
-        <v>58.26533999999999</v>
+        <v>57.96493749999999</v>
       </c>
       <c r="O26">
-        <v>11.0704146</v>
+        <v>11.013338125</v>
       </c>
       <c r="P26">
-        <v>47.1949254</v>
+        <v>46.95159937499999</v>
       </c>
       <c r="Q26">
-        <v>59.59492539999999</v>
+        <v>59.35159937499999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08807981756371405</v>
+        <v>0.08855825640454401</v>
       </c>
       <c r="T26">
-        <v>0.8241123396998346</v>
+        <v>0.8334380032253565</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.081565566198684</v>
+        <v>8.718302943550736</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07725244230340801</v>
+        <v>0.07716382325839334</v>
       </c>
       <c r="C27">
-        <v>437.0036845752693</v>
+        <v>432.115589244093</v>
       </c>
       <c r="D27">
-        <v>577.3786845752693</v>
+        <v>578.105589244093</v>
       </c>
       <c r="E27">
-        <v>-78.625</v>
+        <v>-73.00999999999999</v>
       </c>
       <c r="F27">
-        <v>140.375</v>
+        <v>145.99</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3489,28 +3489,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M27">
-        <v>7.5100625</v>
+        <v>7.810465000000001</v>
       </c>
       <c r="N27">
-        <v>57.96493749999999</v>
+        <v>57.66453499999999</v>
       </c>
       <c r="O27">
-        <v>11.013338125</v>
+        <v>10.95626165</v>
       </c>
       <c r="P27">
-        <v>46.95159937499999</v>
+        <v>46.70827335</v>
       </c>
       <c r="Q27">
-        <v>59.35159937499999</v>
+        <v>59.10827335</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08855825640454401</v>
+        <v>0.08904962602485586</v>
       </c>
       <c r="T27">
-        <v>0.8334380032253565</v>
+        <v>0.8430157117110278</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.718302943550736</v>
+        <v>8.382983599568014</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07716382325839334</v>
+        <v>0.07707520421337866</v>
       </c>
       <c r="C28">
-        <v>432.115589244093</v>
+        <v>427.2293265280789</v>
       </c>
       <c r="D28">
-        <v>578.105589244093</v>
+        <v>578.8343265280789</v>
       </c>
       <c r="E28">
-        <v>-73.00999999999999</v>
+        <v>-67.39499999999998</v>
       </c>
       <c r="F28">
-        <v>145.99</v>
+        <v>151.605</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3571,28 +3571,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M28">
-        <v>7.810465000000001</v>
+        <v>8.110867500000001</v>
       </c>
       <c r="N28">
-        <v>57.66453499999999</v>
+        <v>57.3641325</v>
       </c>
       <c r="O28">
-        <v>10.95626165</v>
+        <v>10.899185175</v>
       </c>
       <c r="P28">
-        <v>46.70827335</v>
+        <v>46.464947325</v>
       </c>
       <c r="Q28">
-        <v>59.10827335</v>
+        <v>58.864947325</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08904962602485586</v>
+        <v>0.08955445782654611</v>
       </c>
       <c r="T28">
-        <v>0.8430157117110278</v>
+        <v>0.8528558231689092</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.382983599568014</v>
+        <v>8.072502725509938</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07707520421337866</v>
+        <v>0.07698658516836399</v>
       </c>
       <c r="C29">
-        <v>427.2293265280789</v>
+        <v>422.3449033663429</v>
       </c>
       <c r="D29">
-        <v>578.8343265280789</v>
+        <v>579.5649033663429</v>
       </c>
       <c r="E29">
-        <v>-67.39499999999998</v>
+        <v>-61.77999999999997</v>
       </c>
       <c r="F29">
-        <v>151.605</v>
+        <v>157.22</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3653,28 +3653,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M29">
-        <v>8.110867500000001</v>
+        <v>8.411270000000002</v>
       </c>
       <c r="N29">
-        <v>57.3641325</v>
+        <v>57.06372999999999</v>
       </c>
       <c r="O29">
-        <v>10.899185175</v>
+        <v>10.8421087</v>
       </c>
       <c r="P29">
-        <v>46.464947325</v>
+        <v>46.2216213</v>
       </c>
       <c r="Q29">
-        <v>58.864947325</v>
+        <v>58.62162129999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08955445782654611</v>
+        <v>0.09007331273383887</v>
       </c>
       <c r="T29">
-        <v>0.8528558231689092</v>
+        <v>0.8629692710561763</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.072502725509938</v>
+        <v>7.784199056741726</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07698658516836399</v>
+        <v>0.07708588612334932</v>
       </c>
       <c r="C30">
-        <v>422.3449033663429</v>
+        <v>415.9113890587154</v>
       </c>
       <c r="D30">
-        <v>579.5649033663429</v>
+        <v>578.7463890587154</v>
       </c>
       <c r="E30">
-        <v>-61.77999999999997</v>
+        <v>-56.16499999999999</v>
       </c>
       <c r="F30">
-        <v>157.22</v>
+        <v>162.835</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3735,45 +3735,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M30">
-        <v>8.411270000000002</v>
+        <v>8.8419405</v>
       </c>
       <c r="N30">
-        <v>57.06372999999999</v>
+        <v>56.63305949999999</v>
       </c>
       <c r="O30">
-        <v>10.8421087</v>
+        <v>10.760281305</v>
       </c>
       <c r="P30">
-        <v>46.2216213</v>
+        <v>45.872778195</v>
       </c>
       <c r="Q30">
-        <v>58.62162129999999</v>
+        <v>58.27277819499999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09007331273383887</v>
+        <v>0.09060678327232299</v>
       </c>
       <c r="T30">
-        <v>0.8629692710561763</v>
+        <v>0.8733676047994228</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.19</v>
       </c>
       <c r="W30">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.784199056741726</v>
+        <v>7.405048699434247</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07708588612334932</v>
+        <v>0.07700374707833464</v>
       </c>
       <c r="C31">
-        <v>415.9113890587154</v>
+        <v>410.9732763478183</v>
       </c>
       <c r="D31">
-        <v>578.7463890587154</v>
+        <v>579.4232763478183</v>
       </c>
       <c r="E31">
-        <v>-56.16500000000002</v>
+        <v>-50.55000000000001</v>
       </c>
       <c r="F31">
-        <v>162.835</v>
+        <v>168.45</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3817,28 +3817,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M31">
-        <v>8.8419405</v>
+        <v>9.146834999999999</v>
       </c>
       <c r="N31">
-        <v>56.63305949999999</v>
+        <v>56.328165</v>
       </c>
       <c r="O31">
-        <v>10.760281305</v>
+        <v>10.70235135</v>
       </c>
       <c r="P31">
-        <v>45.872778195</v>
+        <v>45.62581365</v>
       </c>
       <c r="Q31">
-        <v>58.27277819499999</v>
+        <v>58.02581365</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09060678327232299</v>
+        <v>0.09115549582619235</v>
       </c>
       <c r="T31">
-        <v>0.8733676047994227</v>
+        <v>0.8840630337924761</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.405048699434247</v>
+        <v>7.158213742786439</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07700374707833464</v>
+        <v>0.07692160803331997</v>
       </c>
       <c r="C32">
-        <v>410.9732763478183</v>
+        <v>406.0367488317835</v>
       </c>
       <c r="D32">
-        <v>579.4232763478183</v>
+        <v>580.1017488317835</v>
       </c>
       <c r="E32">
-        <v>-50.55000000000001</v>
+        <v>-44.935</v>
       </c>
       <c r="F32">
-        <v>168.45</v>
+        <v>174.065</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3899,28 +3899,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M32">
-        <v>9.146834999999999</v>
+        <v>9.451729500000001</v>
       </c>
       <c r="N32">
-        <v>56.328165</v>
+        <v>56.0232705</v>
       </c>
       <c r="O32">
-        <v>10.70235135</v>
+        <v>10.644421395</v>
       </c>
       <c r="P32">
-        <v>45.62581365</v>
+        <v>45.378849105</v>
       </c>
       <c r="Q32">
-        <v>58.02581365</v>
+        <v>57.778849105</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09115549582619235</v>
+        <v>0.09172011309176809</v>
       </c>
       <c r="T32">
-        <v>0.8840630337924761</v>
+        <v>0.8950684752201108</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.158213742786439</v>
+        <v>6.927303622051392</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07692160803331997</v>
+        <v>0.07683946898830531</v>
       </c>
       <c r="C33">
-        <v>406.0367488317835</v>
+        <v>401.1018120856648</v>
       </c>
       <c r="D33">
-        <v>580.1017488317835</v>
+        <v>580.7818120856648</v>
       </c>
       <c r="E33">
-        <v>-44.935</v>
+        <v>-39.31999999999999</v>
       </c>
       <c r="F33">
-        <v>174.065</v>
+        <v>179.68</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3981,28 +3981,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M33">
-        <v>9.451729500000001</v>
+        <v>9.756624</v>
       </c>
       <c r="N33">
-        <v>56.0232705</v>
+        <v>55.71837599999999</v>
       </c>
       <c r="O33">
-        <v>10.644421395</v>
+        <v>10.58649144</v>
       </c>
       <c r="P33">
-        <v>45.378849105</v>
+        <v>45.13188456</v>
       </c>
       <c r="Q33">
-        <v>57.778849105</v>
+        <v>57.53188455999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09172011309176809</v>
+        <v>0.0923013367475078</v>
       </c>
       <c r="T33">
-        <v>0.8950684752201108</v>
+        <v>0.9063976061014996</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.927303622051392</v>
+        <v>6.710825383862286</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07683946898830531</v>
+        <v>0.07675732994329063</v>
       </c>
       <c r="C34">
-        <v>401.1018120856648</v>
+        <v>396.1684717106893</v>
       </c>
       <c r="D34">
-        <v>580.7818120856648</v>
+        <v>581.4634717106893</v>
       </c>
       <c r="E34">
-        <v>-39.31999999999999</v>
+        <v>-33.70499999999998</v>
       </c>
       <c r="F34">
-        <v>179.68</v>
+        <v>185.295</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4063,28 +4063,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M34">
-        <v>9.756624</v>
+        <v>10.0615185</v>
       </c>
       <c r="N34">
-        <v>55.71837599999999</v>
+        <v>55.41348149999999</v>
       </c>
       <c r="O34">
-        <v>10.58649144</v>
+        <v>10.528561485</v>
       </c>
       <c r="P34">
-        <v>45.13188456</v>
+        <v>44.88492001499999</v>
       </c>
       <c r="Q34">
-        <v>57.53188455999999</v>
+        <v>57.28492001499999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0923013367475078</v>
+        <v>0.09289991036312034</v>
       </c>
       <c r="T34">
-        <v>0.9063976061014996</v>
+        <v>0.9180649199942729</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.710825383862286</v>
+        <v>6.507467038896761</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07675732994329063</v>
+        <v>0.07667519089827594</v>
       </c>
       <c r="C35">
-        <v>396.1684717106893</v>
+        <v>391.2367333344114</v>
       </c>
       <c r="D35">
-        <v>581.4634717106893</v>
+        <v>582.1467333344115</v>
       </c>
       <c r="E35">
-        <v>-33.70499999999998</v>
+        <v>-28.08999999999997</v>
       </c>
       <c r="F35">
-        <v>185.295</v>
+        <v>190.91</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4145,28 +4145,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M35">
-        <v>10.0615185</v>
+        <v>10.366413</v>
       </c>
       <c r="N35">
-        <v>55.41348149999999</v>
+        <v>55.10858699999999</v>
       </c>
       <c r="O35">
-        <v>10.528561485</v>
+        <v>10.47063153</v>
       </c>
       <c r="P35">
-        <v>44.88492001499999</v>
+        <v>44.63795546999999</v>
       </c>
       <c r="Q35">
-        <v>57.28492001499999</v>
+        <v>57.03795546999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09289991036312034</v>
+        <v>0.09351662257314539</v>
       </c>
       <c r="T35">
-        <v>0.9180649199942729</v>
+        <v>0.9300857888534939</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.507467038896761</v>
+        <v>6.316070949517445</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07667519089827594</v>
+        <v>0.07659305185326128</v>
       </c>
       <c r="C36">
-        <v>391.2367333344114</v>
+        <v>386.3066026108679</v>
       </c>
       <c r="D36">
-        <v>582.1467333344115</v>
+        <v>582.8316026108679</v>
       </c>
       <c r="E36">
-        <v>-28.08999999999997</v>
+        <v>-22.47499999999999</v>
       </c>
       <c r="F36">
-        <v>190.91</v>
+        <v>196.525</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4227,28 +4227,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M36">
-        <v>10.366413</v>
+        <v>10.6713075</v>
       </c>
       <c r="N36">
-        <v>55.10858699999999</v>
+        <v>54.8036925</v>
       </c>
       <c r="O36">
-        <v>10.47063153</v>
+        <v>10.412701575</v>
       </c>
       <c r="P36">
-        <v>44.63795546999999</v>
+        <v>44.390990925</v>
       </c>
       <c r="Q36">
-        <v>57.03795546999999</v>
+        <v>56.790990925</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09351662257314539</v>
+        <v>0.0941523105434789</v>
       </c>
       <c r="T36">
-        <v>0.9300857888534939</v>
+        <v>0.9424765306006909</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.316070949517445</v>
+        <v>6.135611779531233</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07659305185326128</v>
+        <v>0.07680251280824663</v>
       </c>
       <c r="C37">
-        <v>386.3066026108679</v>
+        <v>378.9483080049589</v>
       </c>
       <c r="D37">
-        <v>582.8316026108679</v>
+        <v>581.0883080049589</v>
       </c>
       <c r="E37">
-        <v>-22.47499999999999</v>
+        <v>-16.85999999999999</v>
       </c>
       <c r="F37">
-        <v>196.525</v>
+        <v>202.14</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4309,45 +4309,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M37">
-        <v>10.6713075</v>
+        <v>11.178342</v>
       </c>
       <c r="N37">
-        <v>54.8036925</v>
+        <v>54.29665799999999</v>
       </c>
       <c r="O37">
-        <v>10.412701575</v>
+        <v>10.31636502</v>
       </c>
       <c r="P37">
-        <v>44.390990925</v>
+        <v>43.98029297999999</v>
       </c>
       <c r="Q37">
-        <v>56.790990925</v>
+        <v>56.38029297999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0941523105434789</v>
+        <v>0.09480786376288534</v>
       </c>
       <c r="T37">
-        <v>0.9424765306006909</v>
+        <v>0.9552544830274881</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.19</v>
       </c>
       <c r="W37">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.135611779531233</v>
+        <v>5.857308713582031</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07680251280824661</v>
+        <v>0.07672847376323194</v>
       </c>
       <c r="C38">
-        <v>378.948308004959</v>
+        <v>373.9483247908419</v>
       </c>
       <c r="D38">
-        <v>581.088308004959</v>
+        <v>581.7033247908419</v>
       </c>
       <c r="E38">
-        <v>-16.86000000000001</v>
+        <v>-11.245</v>
       </c>
       <c r="F38">
-        <v>202.14</v>
+        <v>207.755</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4391,28 +4391,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M38">
-        <v>11.178342</v>
+        <v>11.4888515</v>
       </c>
       <c r="N38">
-        <v>54.29665799999999</v>
+        <v>53.98614849999999</v>
       </c>
       <c r="O38">
-        <v>10.31636502</v>
+        <v>10.257368215</v>
       </c>
       <c r="P38">
-        <v>43.98029297999999</v>
+        <v>43.72878028499999</v>
       </c>
       <c r="Q38">
-        <v>56.38029297999999</v>
+        <v>56.12878028499999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09480786376288533</v>
+        <v>0.09548422819560626</v>
       </c>
       <c r="T38">
-        <v>0.9552544830274878</v>
+        <v>0.9684380847376753</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.857308713582032</v>
+        <v>5.699003072674409</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07672847376323194</v>
+        <v>0.07665443471821728</v>
       </c>
       <c r="C39">
-        <v>373.9483247908419</v>
+        <v>368.9496448085963</v>
       </c>
       <c r="D39">
-        <v>581.7033247908419</v>
+        <v>582.3196448085963</v>
       </c>
       <c r="E39">
-        <v>-11.245</v>
+        <v>-5.629999999999995</v>
       </c>
       <c r="F39">
-        <v>207.755</v>
+        <v>213.37</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4473,28 +4473,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M39">
-        <v>11.4888515</v>
+        <v>11.799361</v>
       </c>
       <c r="N39">
-        <v>53.98614849999999</v>
+        <v>53.67563899999999</v>
       </c>
       <c r="O39">
-        <v>10.257368215</v>
+        <v>10.19837141</v>
       </c>
       <c r="P39">
-        <v>43.72878028499999</v>
+        <v>43.47726758999999</v>
       </c>
       <c r="Q39">
-        <v>56.12878028499999</v>
+        <v>55.87726758999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09548422819560626</v>
+        <v>0.09618241083583431</v>
       </c>
       <c r="T39">
-        <v>0.9684380847376753</v>
+        <v>0.9820469639223849</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.699003072674409</v>
+        <v>5.549029307604029</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07665443471821728</v>
+        <v>0.0765803956732026</v>
       </c>
       <c r="C40">
-        <v>368.9496448085963</v>
+        <v>363.9522722049747</v>
       </c>
       <c r="D40">
-        <v>582.3196448085963</v>
+        <v>582.9372722049748</v>
       </c>
       <c r="E40">
-        <v>-5.629999999999995</v>
+        <v>-0.01499999999998636</v>
       </c>
       <c r="F40">
-        <v>213.37</v>
+        <v>218.985</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4555,28 +4555,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M40">
-        <v>11.799361</v>
+        <v>12.1098705</v>
       </c>
       <c r="N40">
-        <v>53.67563899999999</v>
+        <v>53.36512949999999</v>
       </c>
       <c r="O40">
-        <v>10.19837141</v>
+        <v>10.139374605</v>
       </c>
       <c r="P40">
-        <v>43.47726758999999</v>
+        <v>43.22575489499999</v>
       </c>
       <c r="Q40">
-        <v>55.87726758999999</v>
+        <v>55.62575489499999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09618241083583431</v>
+        <v>0.0969034847101682</v>
       </c>
       <c r="T40">
-        <v>0.9820469639223849</v>
+        <v>0.9961020358672489</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.549029307604029</v>
+        <v>5.406746504844952</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0765803956732026</v>
+        <v>0.07650635662818793</v>
       </c>
       <c r="C41">
-        <v>363.9522722049747</v>
+        <v>358.9562111443402</v>
       </c>
       <c r="D41">
-        <v>582.9372722049748</v>
+        <v>583.5562111443402</v>
       </c>
       <c r="E41">
-        <v>-0.01499999999998636</v>
+        <v>5.600000000000023</v>
       </c>
       <c r="F41">
-        <v>218.985</v>
+        <v>224.6</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4637,28 +4637,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M41">
-        <v>12.1098705</v>
+        <v>12.42038</v>
       </c>
       <c r="N41">
-        <v>53.36512949999999</v>
+        <v>53.05461999999999</v>
       </c>
       <c r="O41">
-        <v>10.139374605</v>
+        <v>10.0803778</v>
       </c>
       <c r="P41">
-        <v>43.22575489499999</v>
+        <v>42.97424219999999</v>
       </c>
       <c r="Q41">
-        <v>55.62575489499999</v>
+        <v>55.37424219999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0969034847101682</v>
+        <v>0.0976485943803132</v>
       </c>
       <c r="T41">
-        <v>0.9961020358672489</v>
+        <v>1.010625610210275</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.406746504844952</v>
+        <v>5.271577842223828</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07650635662818793</v>
+        <v>0.07643231758317325</v>
       </c>
       <c r="C42">
-        <v>358.9562111443402</v>
+        <v>353.9614658087612</v>
       </c>
       <c r="D42">
-        <v>583.5562111443402</v>
+        <v>584.1764658087612</v>
       </c>
       <c r="E42">
-        <v>5.600000000000023</v>
+        <v>11.215</v>
       </c>
       <c r="F42">
-        <v>224.6</v>
+        <v>230.215</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4719,28 +4719,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M42">
-        <v>12.42038</v>
+        <v>12.7308895</v>
       </c>
       <c r="N42">
-        <v>53.05461999999999</v>
+        <v>52.74411049999999</v>
       </c>
       <c r="O42">
-        <v>10.0803778</v>
+        <v>10.021380995</v>
       </c>
       <c r="P42">
-        <v>42.97424219999999</v>
+        <v>42.72272950499999</v>
       </c>
       <c r="Q42">
-        <v>55.37424219999999</v>
+        <v>55.12272950499999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0976485943803132</v>
+        <v>0.09841896200537839</v>
       </c>
       <c r="T42">
-        <v>1.010625610210275</v>
+        <v>1.025641509107302</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.271577842223828</v>
+        <v>5.143002772901296</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07643231758317325</v>
+        <v>0.07635827853815857</v>
       </c>
       <c r="C43">
-        <v>353.9614658087612</v>
+        <v>348.968040398105</v>
       </c>
       <c r="D43">
-        <v>584.1764658087612</v>
+        <v>584.7980403981051</v>
       </c>
       <c r="E43">
-        <v>11.215</v>
+        <v>16.83000000000001</v>
       </c>
       <c r="F43">
-        <v>230.215</v>
+        <v>235.83</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4801,28 +4801,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M43">
-        <v>12.7308895</v>
+        <v>13.041399</v>
       </c>
       <c r="N43">
-        <v>52.74411049999999</v>
+        <v>52.433601</v>
       </c>
       <c r="O43">
-        <v>10.021380995</v>
+        <v>9.96238419</v>
       </c>
       <c r="P43">
-        <v>42.72272950499999</v>
+        <v>42.47121680999999</v>
       </c>
       <c r="Q43">
-        <v>55.12272950499999</v>
+        <v>54.87121680999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09841896200537839</v>
+        <v>0.0992158940313079</v>
       </c>
       <c r="T43">
-        <v>1.025641509107302</v>
+        <v>1.041175197621468</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.143002772901296</v>
+        <v>5.020550325927455</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07635827853815859</v>
+        <v>0.07628423949314392</v>
       </c>
       <c r="C44">
-        <v>348.968040398105</v>
+        <v>343.9759391301333</v>
       </c>
       <c r="D44">
-        <v>584.7980403981049</v>
+        <v>585.4209391301333</v>
       </c>
       <c r="E44">
-        <v>16.82999999999998</v>
+        <v>22.44499999999999</v>
       </c>
       <c r="F44">
-        <v>235.83</v>
+        <v>241.445</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4883,28 +4883,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M44">
-        <v>13.041399</v>
+        <v>13.3519085</v>
       </c>
       <c r="N44">
-        <v>52.433601</v>
+        <v>52.12309149999999</v>
       </c>
       <c r="O44">
-        <v>9.96238419</v>
+        <v>9.903387384999998</v>
       </c>
       <c r="P44">
-        <v>42.47121680999999</v>
+        <v>42.219704115</v>
       </c>
       <c r="Q44">
-        <v>54.87121680999999</v>
+        <v>54.619704115</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0992158940313079</v>
+        <v>0.100040788584463</v>
       </c>
       <c r="T44">
-        <v>1.041175197621468</v>
+        <v>1.057253927837885</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.020550325927456</v>
+        <v>4.903793341603562</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07628423949314392</v>
+        <v>0.07621020044812925</v>
       </c>
       <c r="C45">
-        <v>343.9759391301333</v>
+        <v>338.9851662405974</v>
       </c>
       <c r="D45">
-        <v>585.4209391301333</v>
+        <v>586.0451662405974</v>
       </c>
       <c r="E45">
-        <v>22.44499999999999</v>
+        <v>28.06</v>
       </c>
       <c r="F45">
-        <v>241.445</v>
+        <v>247.06</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4965,28 +4965,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M45">
-        <v>13.3519085</v>
+        <v>13.662418</v>
       </c>
       <c r="N45">
-        <v>52.12309149999999</v>
+        <v>51.81258199999999</v>
       </c>
       <c r="O45">
-        <v>9.903387384999998</v>
+        <v>9.844390579999999</v>
       </c>
       <c r="P45">
-        <v>42.219704115</v>
+        <v>41.96819142</v>
       </c>
       <c r="Q45">
-        <v>54.619704115</v>
+        <v>54.36819142</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.100040788584463</v>
+        <v>0.1008951436573736</v>
       </c>
       <c r="T45">
-        <v>1.057253927837885</v>
+        <v>1.073906898419174</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.903793341603562</v>
+        <v>4.792343492930753</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07621020044812925</v>
+        <v>0.07613616140311458</v>
       </c>
       <c r="C46">
-        <v>338.9851662405974</v>
+        <v>333.995725983333</v>
       </c>
       <c r="D46">
-        <v>586.0451662405974</v>
+        <v>586.670725983333</v>
       </c>
       <c r="E46">
-        <v>28.06</v>
+        <v>33.67500000000001</v>
       </c>
       <c r="F46">
-        <v>247.06</v>
+        <v>252.675</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5047,28 +5047,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M46">
-        <v>13.662418</v>
+        <v>13.9729275</v>
       </c>
       <c r="N46">
-        <v>51.81258199999999</v>
+        <v>51.5020725</v>
       </c>
       <c r="O46">
-        <v>9.844390579999999</v>
+        <v>9.785393774999999</v>
       </c>
       <c r="P46">
-        <v>41.96819142</v>
+        <v>41.71667872499999</v>
       </c>
       <c r="Q46">
-        <v>54.36819142</v>
+        <v>54.11667872499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1008951436573736</v>
+        <v>0.101780566187481</v>
       </c>
       <c r="T46">
-        <v>1.073906898419174</v>
+        <v>1.091165431567056</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.792343492930753</v>
+        <v>4.685846970865626</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07613616140311458</v>
+        <v>0.07606212235809989</v>
       </c>
       <c r="C47">
-        <v>333.995725983333</v>
+        <v>329.007622630359</v>
       </c>
       <c r="D47">
-        <v>586.670725983333</v>
+        <v>587.297622630359</v>
       </c>
       <c r="E47">
-        <v>33.67500000000001</v>
+        <v>39.29000000000002</v>
       </c>
       <c r="F47">
-        <v>252.675</v>
+        <v>258.29</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5129,28 +5129,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M47">
-        <v>13.9729275</v>
+        <v>14.283437</v>
       </c>
       <c r="N47">
-        <v>51.5020725</v>
+        <v>51.191563</v>
       </c>
       <c r="O47">
-        <v>9.785393774999999</v>
+        <v>9.72639697</v>
       </c>
       <c r="P47">
-        <v>41.71667872499999</v>
+        <v>41.46516602999999</v>
       </c>
       <c r="Q47">
-        <v>54.11667872499999</v>
+        <v>53.86516602999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.101780566187481</v>
+        <v>0.1026987821446294</v>
       </c>
       <c r="T47">
-        <v>1.091165431567056</v>
+        <v>1.109063169646341</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.685846970865626</v>
+        <v>4.583980732368547</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07606212235809989</v>
+        <v>0.07693983331308522</v>
       </c>
       <c r="C48">
-        <v>329.007622630359</v>
+        <v>316.0460700119218</v>
       </c>
       <c r="D48">
-        <v>587.297622630359</v>
+        <v>579.9510700119218</v>
       </c>
       <c r="E48">
-        <v>39.29000000000002</v>
+        <v>44.90500000000003</v>
       </c>
       <c r="F48">
-        <v>258.29</v>
+        <v>263.905</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5211,45 +5211,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M48">
-        <v>14.283437</v>
+        <v>15.253709</v>
       </c>
       <c r="N48">
-        <v>51.191563</v>
+        <v>50.22129099999999</v>
       </c>
       <c r="O48">
-        <v>9.72639697</v>
+        <v>9.542045289999999</v>
       </c>
       <c r="P48">
-        <v>41.46516602999999</v>
+        <v>40.67924571</v>
       </c>
       <c r="Q48">
-        <v>53.86516602999999</v>
+        <v>53.07924571</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1026987821446294</v>
+        <v>0.1036516477605381</v>
       </c>
       <c r="T48">
-        <v>1.109063169646341</v>
+        <v>1.12763629406824</v>
       </c>
       <c r="U48">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.19</v>
       </c>
       <c r="W48">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.583980732368547</v>
+        <v>4.292398655304096</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07693983331308522</v>
+        <v>0.07688604426807055</v>
       </c>
       <c r="C49">
-        <v>316.0460700119218</v>
+        <v>310.8760004082511</v>
       </c>
       <c r="D49">
-        <v>579.9510700119218</v>
+        <v>580.3960004082511</v>
       </c>
       <c r="E49">
-        <v>44.90500000000003</v>
+        <v>50.52000000000004</v>
       </c>
       <c r="F49">
-        <v>263.905</v>
+        <v>269.52</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5293,28 +5293,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M49">
-        <v>15.253709</v>
+        <v>15.578256</v>
       </c>
       <c r="N49">
-        <v>50.22129099999999</v>
+        <v>49.89674399999999</v>
       </c>
       <c r="O49">
-        <v>9.542045289999999</v>
+        <v>9.480381359999999</v>
       </c>
       <c r="P49">
-        <v>40.67924571</v>
+        <v>40.41636263999999</v>
       </c>
       <c r="Q49">
-        <v>53.07924571</v>
+        <v>52.81636263999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1036516477605381</v>
+        <v>0.1046411620539818</v>
       </c>
       <c r="T49">
-        <v>1.12763629406824</v>
+        <v>1.146923769429443</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.292398655304096</v>
+        <v>4.202973683318594</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07688604426807055</v>
+        <v>0.07683225522305587</v>
       </c>
       <c r="C50">
-        <v>310.8760004082511</v>
+        <v>305.706614017558</v>
       </c>
       <c r="D50">
-        <v>580.3960004082511</v>
+        <v>580.841614017558</v>
       </c>
       <c r="E50">
-        <v>50.51999999999998</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="F50">
-        <v>269.52</v>
+        <v>275.135</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5375,28 +5375,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M50">
-        <v>15.578256</v>
+        <v>15.902803</v>
       </c>
       <c r="N50">
-        <v>49.896744</v>
+        <v>49.572197</v>
       </c>
       <c r="O50">
-        <v>9.480381359999999</v>
+        <v>9.418717429999999</v>
       </c>
       <c r="P50">
-        <v>40.41636264</v>
+        <v>40.15347956999999</v>
       </c>
       <c r="Q50">
-        <v>52.81636264</v>
+        <v>52.55347956999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1046411620539818</v>
+        <v>0.1056694808295213</v>
       </c>
       <c r="T50">
-        <v>1.146923769429443</v>
+        <v>1.166967616373438</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.202973683318595</v>
+        <v>4.117198710189644</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07683225522305587</v>
+        <v>0.07677846617804121</v>
       </c>
       <c r="C51">
-        <v>305.706614017558</v>
+        <v>300.537912414713</v>
       </c>
       <c r="D51">
-        <v>580.841614017558</v>
+        <v>581.287912414713</v>
       </c>
       <c r="E51">
-        <v>56.13499999999999</v>
+        <v>61.75</v>
       </c>
       <c r="F51">
-        <v>275.135</v>
+        <v>280.75</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5457,28 +5457,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M51">
-        <v>15.902803</v>
+        <v>16.22735</v>
       </c>
       <c r="N51">
-        <v>49.572197</v>
+        <v>49.24764999999999</v>
       </c>
       <c r="O51">
-        <v>9.418717429999999</v>
+        <v>9.357053499999999</v>
       </c>
       <c r="P51">
-        <v>40.15347956999999</v>
+        <v>39.89059649999999</v>
       </c>
       <c r="Q51">
-        <v>52.55347956999999</v>
+        <v>52.29059649999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1056694808295213</v>
+        <v>0.1067389323560824</v>
       </c>
       <c r="T51">
-        <v>1.166967616373438</v>
+        <v>1.187813217195193</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.117198710189644</v>
+        <v>4.03485473598585</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07677846617804121</v>
+        <v>0.07817052713302654</v>
       </c>
       <c r="C52">
-        <v>300.537912414713</v>
+        <v>283.589205322332</v>
       </c>
       <c r="D52">
-        <v>581.287912414713</v>
+        <v>569.954205322332</v>
       </c>
       <c r="E52">
-        <v>61.75</v>
+        <v>67.36500000000001</v>
       </c>
       <c r="F52">
-        <v>280.75</v>
+        <v>286.365</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5539,45 +5539,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M52">
-        <v>16.22735</v>
+        <v>17.5541745</v>
       </c>
       <c r="N52">
-        <v>49.24764999999999</v>
+        <v>47.92082549999999</v>
       </c>
       <c r="O52">
-        <v>9.357053499999999</v>
+        <v>9.104956844999998</v>
       </c>
       <c r="P52">
-        <v>39.89059649999999</v>
+        <v>38.815868655</v>
       </c>
       <c r="Q52">
-        <v>52.29059649999999</v>
+        <v>51.21586865499999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1067389323560824</v>
+        <v>0.1078520349653603</v>
       </c>
       <c r="T52">
-        <v>1.187813217195193</v>
+        <v>1.209509658866816</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.19</v>
       </c>
       <c r="W52">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.03485473598585</v>
+        <v>3.729882028915685</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07817052713302654</v>
+        <v>0.07814508808801186</v>
       </c>
       <c r="C53">
-        <v>283.589205322332</v>
+        <v>278.1773558597658</v>
       </c>
       <c r="D53">
-        <v>569.954205322332</v>
+        <v>570.1573558597659</v>
       </c>
       <c r="E53">
-        <v>67.36500000000001</v>
+        <v>72.98000000000002</v>
       </c>
       <c r="F53">
-        <v>286.365</v>
+        <v>291.98</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5621,28 +5621,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M53">
-        <v>17.5541745</v>
+        <v>17.898374</v>
       </c>
       <c r="N53">
-        <v>47.92082549999999</v>
+        <v>47.57662599999999</v>
       </c>
       <c r="O53">
-        <v>9.104956844999998</v>
+        <v>9.039558939999997</v>
       </c>
       <c r="P53">
-        <v>38.815868655</v>
+        <v>38.53706705999999</v>
       </c>
       <c r="Q53">
-        <v>51.21586865499999</v>
+        <v>50.93706705999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1078520349653603</v>
+        <v>0.1090115168500247</v>
       </c>
       <c r="T53">
-        <v>1.209509658866816</v>
+        <v>1.232110118941423</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.729882028915685</v>
+        <v>3.658153528359615</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07814508808801186</v>
+        <v>0.0781196490429972</v>
       </c>
       <c r="C54">
-        <v>278.1773558597658</v>
+        <v>272.7656512679832</v>
       </c>
       <c r="D54">
-        <v>570.1573558597659</v>
+        <v>570.3606512679833</v>
       </c>
       <c r="E54">
-        <v>72.98000000000002</v>
+        <v>78.59500000000003</v>
       </c>
       <c r="F54">
-        <v>291.98</v>
+        <v>297.595</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5703,28 +5703,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M54">
-        <v>17.898374</v>
+        <v>18.2425735</v>
       </c>
       <c r="N54">
-        <v>47.57662599999999</v>
+        <v>47.23242649999999</v>
       </c>
       <c r="O54">
-        <v>9.039558939999997</v>
+        <v>8.974161034999998</v>
       </c>
       <c r="P54">
-        <v>38.53706705999999</v>
+        <v>38.25826546499999</v>
       </c>
       <c r="Q54">
-        <v>50.93706705999999</v>
+        <v>50.65826546499999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1090115168500247</v>
+        <v>0.1102203383893557</v>
       </c>
       <c r="T54">
-        <v>1.232110118941423</v>
+        <v>1.255672300721332</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.658153528359615</v>
+        <v>3.589131763673584</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0781196490429972</v>
+        <v>0.07809420999798253</v>
       </c>
       <c r="C55">
-        <v>272.7656512679832</v>
+        <v>267.3540917020049</v>
       </c>
       <c r="D55">
-        <v>570.3606512679833</v>
+        <v>570.5640917020049</v>
       </c>
       <c r="E55">
-        <v>78.59500000000003</v>
+        <v>84.21000000000004</v>
       </c>
       <c r="F55">
-        <v>297.595</v>
+        <v>303.21</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5785,28 +5785,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M55">
-        <v>18.2425735</v>
+        <v>18.586773</v>
       </c>
       <c r="N55">
-        <v>47.23242649999999</v>
+        <v>46.88822699999999</v>
       </c>
       <c r="O55">
-        <v>8.974161034999998</v>
+        <v>8.908763129999999</v>
       </c>
       <c r="P55">
-        <v>38.25826546499999</v>
+        <v>37.97946387</v>
       </c>
       <c r="Q55">
-        <v>50.65826546499999</v>
+        <v>50.37946387</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1102203383893557</v>
+        <v>0.1114817173869185</v>
       </c>
       <c r="T55">
-        <v>1.255672300721332</v>
+        <v>1.280258925187325</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.589131763673584</v>
+        <v>3.522666360642592</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07809420999798253</v>
+        <v>0.07931617095296783</v>
       </c>
       <c r="C56">
-        <v>267.3540917020049</v>
+        <v>252.1280435831543</v>
       </c>
       <c r="D56">
-        <v>570.5640917020049</v>
+        <v>560.9530435831543</v>
       </c>
       <c r="E56">
-        <v>84.21000000000004</v>
+        <v>89.82500000000005</v>
       </c>
       <c r="F56">
-        <v>303.21</v>
+        <v>308.825</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5867,45 +5867,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M56">
-        <v>18.586773</v>
+        <v>19.79568250000001</v>
       </c>
       <c r="N56">
-        <v>46.88822699999999</v>
+        <v>45.67931749999999</v>
       </c>
       <c r="O56">
-        <v>8.908763129999999</v>
+        <v>8.679070324999998</v>
       </c>
       <c r="P56">
-        <v>37.97946387</v>
+        <v>37.00024717499999</v>
       </c>
       <c r="Q56">
-        <v>50.37946387</v>
+        <v>49.40024717499999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1114817173869185</v>
+        <v>0.1127991576732619</v>
       </c>
       <c r="T56">
-        <v>1.280258925187325</v>
+        <v>1.305938288518472</v>
       </c>
       <c r="U56">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.19</v>
       </c>
       <c r="W56">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.522666360642592</v>
+        <v>3.307539409161567</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07931617095296783</v>
+        <v>0.07931341190795319</v>
       </c>
       <c r="C57">
-        <v>252.1280435831543</v>
+        <v>246.5343794749132</v>
       </c>
       <c r="D57">
-        <v>560.9530435831543</v>
+        <v>560.9743794749132</v>
       </c>
       <c r="E57">
-        <v>89.82500000000005</v>
+        <v>95.44000000000005</v>
       </c>
       <c r="F57">
-        <v>308.825</v>
+        <v>314.4400000000001</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5949,28 +5949,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M57">
-        <v>19.79568250000001</v>
+        <v>20.155604</v>
       </c>
       <c r="N57">
-        <v>45.67931749999999</v>
+        <v>45.31939599999999</v>
       </c>
       <c r="O57">
-        <v>8.679070324999998</v>
+        <v>8.610685239999999</v>
       </c>
       <c r="P57">
-        <v>37.00024717499999</v>
+        <v>36.70871075999999</v>
       </c>
       <c r="Q57">
-        <v>49.40024717499999</v>
+        <v>49.10871075999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1127991576732619</v>
+        <v>0.1141764816089845</v>
       </c>
       <c r="T57">
-        <v>1.305938288518472</v>
+        <v>1.332784895637399</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.307539409161567</v>
+        <v>3.248476205426539</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07931341190795319</v>
+        <v>0.07931065286293849</v>
       </c>
       <c r="C58">
-        <v>246.5343794749132</v>
+        <v>240.9407169897588</v>
       </c>
       <c r="D58">
-        <v>560.9743794749132</v>
+        <v>560.9957169897588</v>
       </c>
       <c r="E58">
-        <v>95.44000000000005</v>
+        <v>101.055</v>
       </c>
       <c r="F58">
-        <v>314.4400000000001</v>
+        <v>320.055</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6031,28 +6031,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M58">
-        <v>20.155604</v>
+        <v>20.5155255</v>
       </c>
       <c r="N58">
-        <v>45.31939599999999</v>
+        <v>44.95947449999999</v>
       </c>
       <c r="O58">
-        <v>8.610685239999999</v>
+        <v>8.542300154999998</v>
       </c>
       <c r="P58">
-        <v>36.70871075999999</v>
+        <v>36.41717434499999</v>
       </c>
       <c r="Q58">
-        <v>49.10871075999999</v>
+        <v>48.81717434499999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1141764816089845</v>
+        <v>0.1156178671231128</v>
       </c>
       <c r="T58">
-        <v>1.332784895637399</v>
+        <v>1.360880182157207</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.248476205426539</v>
+        <v>3.191485394805022</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07931065286293849</v>
+        <v>0.07930789381792383</v>
       </c>
       <c r="C59">
-        <v>240.9407169897588</v>
+        <v>235.3470561278755</v>
       </c>
       <c r="D59">
-        <v>560.9957169897588</v>
+        <v>561.0170561278755</v>
       </c>
       <c r="E59">
-        <v>101.055</v>
+        <v>106.67</v>
       </c>
       <c r="F59">
-        <v>320.055</v>
+        <v>325.67</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6113,28 +6113,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M59">
-        <v>20.5155255</v>
+        <v>20.875447</v>
       </c>
       <c r="N59">
-        <v>44.95947449999999</v>
+        <v>44.59955299999999</v>
       </c>
       <c r="O59">
-        <v>8.542300154999998</v>
+        <v>8.473915069999999</v>
       </c>
       <c r="P59">
-        <v>36.41717434499999</v>
+        <v>36.12563793</v>
       </c>
       <c r="Q59">
-        <v>48.81717434499999</v>
+        <v>48.52563792999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1156178671231128</v>
+        <v>0.1171278900426758</v>
       </c>
       <c r="T59">
-        <v>1.360880182157207</v>
+        <v>1.390313339463672</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.191485394805022</v>
+        <v>3.136459784549763</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07930789381792383</v>
+        <v>0.07930513477290917</v>
       </c>
       <c r="C60">
-        <v>235.3470561278756</v>
+        <v>229.7533968894492</v>
       </c>
       <c r="D60">
-        <v>561.0170561278755</v>
+        <v>561.0383968894491</v>
       </c>
       <c r="E60">
-        <v>106.67</v>
+        <v>112.285</v>
       </c>
       <c r="F60">
-        <v>325.67</v>
+        <v>331.285</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6195,28 +6195,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M60">
-        <v>20.875447</v>
+        <v>21.2353685</v>
       </c>
       <c r="N60">
-        <v>44.599553</v>
+        <v>44.23963149999999</v>
       </c>
       <c r="O60">
-        <v>8.47391507</v>
+        <v>8.405529984999999</v>
       </c>
       <c r="P60">
-        <v>36.12563793</v>
+        <v>35.83410151499999</v>
       </c>
       <c r="Q60">
-        <v>48.52563792999999</v>
+        <v>48.23410151499999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1171278900426758</v>
+        <v>0.1187115726168516</v>
       </c>
       <c r="T60">
-        <v>1.390313339463671</v>
+        <v>1.421182260541183</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.136459784549763</v>
+        <v>3.083299449218411</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07930513477290917</v>
+        <v>0.07930237572789449</v>
       </c>
       <c r="C61">
-        <v>229.7533968894492</v>
+        <v>224.1597392746647</v>
       </c>
       <c r="D61">
-        <v>561.0383968894491</v>
+        <v>561.0597392746647</v>
       </c>
       <c r="E61">
-        <v>112.285</v>
+        <v>117.9</v>
       </c>
       <c r="F61">
-        <v>331.285</v>
+        <v>336.9</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6277,28 +6277,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M61">
-        <v>21.2353685</v>
+        <v>21.59529</v>
       </c>
       <c r="N61">
-        <v>44.23963149999999</v>
+        <v>43.87971</v>
       </c>
       <c r="O61">
-        <v>8.405529984999999</v>
+        <v>8.337144899999998</v>
       </c>
       <c r="P61">
-        <v>35.83410151499999</v>
+        <v>35.5425651</v>
       </c>
       <c r="Q61">
-        <v>48.23410151499999</v>
+        <v>47.9425651</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1187115726168516</v>
+        <v>0.1203744393197362</v>
       </c>
       <c r="T61">
-        <v>1.421182260541183</v>
+        <v>1.453594627672571</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.083299449218411</v>
+        <v>3.031911125064771</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07930237572789449</v>
+        <v>0.08315359668287982</v>
       </c>
       <c r="C62">
-        <v>224.1597392746647</v>
+        <v>190.2549482723148</v>
       </c>
       <c r="D62">
-        <v>561.0597392746647</v>
+        <v>532.7699482723148</v>
       </c>
       <c r="E62">
-        <v>117.9</v>
+        <v>123.515</v>
       </c>
       <c r="F62">
-        <v>336.9</v>
+        <v>342.515</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6359,45 +6359,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M62">
-        <v>21.59529</v>
+        <v>24.6268285</v>
       </c>
       <c r="N62">
-        <v>43.87971</v>
+        <v>40.84817149999999</v>
       </c>
       <c r="O62">
-        <v>8.337144899999998</v>
+        <v>7.761152584999999</v>
       </c>
       <c r="P62">
-        <v>35.5425651</v>
+        <v>33.08701891499999</v>
       </c>
       <c r="Q62">
-        <v>47.9425651</v>
+        <v>45.48701891499999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1203744393197362</v>
+        <v>0.1221225812381534</v>
       </c>
       <c r="T62">
-        <v>1.453594627672571</v>
+        <v>1.487669167477363</v>
       </c>
       <c r="U62">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V62">
         <v>0.19</v>
       </c>
       <c r="W62">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.031911125064771</v>
+        <v>2.658685831186098</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08315359668287982</v>
+        <v>0.08321401763786515</v>
       </c>
       <c r="C63">
-        <v>190.2549482723148</v>
+        <v>184.2188280614728</v>
       </c>
       <c r="D63">
-        <v>532.7699482723148</v>
+        <v>532.3488280614728</v>
       </c>
       <c r="E63">
-        <v>123.515</v>
+        <v>129.13</v>
       </c>
       <c r="F63">
-        <v>342.515</v>
+        <v>348.13</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6441,28 +6441,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M63">
-        <v>24.6268285</v>
+        <v>25.030547</v>
       </c>
       <c r="N63">
-        <v>40.84817149999999</v>
+        <v>40.444453</v>
       </c>
       <c r="O63">
-        <v>7.761152584999999</v>
+        <v>7.684446069999999</v>
       </c>
       <c r="P63">
-        <v>33.08701891499999</v>
+        <v>32.76000693</v>
       </c>
       <c r="Q63">
-        <v>45.48701891499999</v>
+        <v>45.16000692999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1221225812381534</v>
+        <v>0.1239627306259609</v>
       </c>
       <c r="T63">
-        <v>1.487669167477363</v>
+        <v>1.523537104113986</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.658685831186098</v>
+        <v>2.615803801650839</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08321401763786515</v>
+        <v>0.08327443859285047</v>
       </c>
       <c r="C64">
-        <v>184.2188280614728</v>
+        <v>178.1833730614435</v>
       </c>
       <c r="D64">
-        <v>532.3488280614728</v>
+        <v>531.9283730614435</v>
       </c>
       <c r="E64">
-        <v>129.13</v>
+        <v>134.745</v>
       </c>
       <c r="F64">
-        <v>348.13</v>
+        <v>353.745</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6523,28 +6523,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M64">
-        <v>25.030547</v>
+        <v>25.4342655</v>
       </c>
       <c r="N64">
-        <v>40.444453</v>
+        <v>40.04073449999999</v>
       </c>
       <c r="O64">
-        <v>7.684446069999999</v>
+        <v>7.607739554999998</v>
       </c>
       <c r="P64">
-        <v>32.76000693</v>
+        <v>32.43299494499999</v>
       </c>
       <c r="Q64">
-        <v>45.16000692999999</v>
+        <v>44.83299494499999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1239627306259609</v>
+        <v>0.1259023475482445</v>
       </c>
       <c r="T64">
-        <v>1.523537104113986</v>
+        <v>1.561343848136372</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.615803801650839</v>
+        <v>2.574283106386539</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08327443859285047</v>
+        <v>0.0833348595478358</v>
       </c>
       <c r="C65">
-        <v>178.1833730614435</v>
+        <v>172.148581697298</v>
       </c>
       <c r="D65">
-        <v>531.9283730614435</v>
+        <v>531.508581697298</v>
       </c>
       <c r="E65">
-        <v>134.745</v>
+        <v>140.36</v>
       </c>
       <c r="F65">
-        <v>353.745</v>
+        <v>359.36</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6605,28 +6605,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M65">
-        <v>25.4342655</v>
+        <v>25.837984</v>
       </c>
       <c r="N65">
-        <v>40.04073449999999</v>
+        <v>39.63701599999999</v>
       </c>
       <c r="O65">
-        <v>7.607739554999998</v>
+        <v>7.531033039999998</v>
       </c>
       <c r="P65">
-        <v>32.43299494499999</v>
+        <v>32.10598295999999</v>
       </c>
       <c r="Q65">
-        <v>44.83299494499999</v>
+        <v>44.50598295999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1259023475482445</v>
+        <v>0.1279497209662105</v>
       </c>
       <c r="T65">
-        <v>1.561343848136372</v>
+        <v>1.601250966826669</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.574283106386539</v>
+        <v>2.534059932849249</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0833348595478358</v>
+        <v>0.08544863050282112</v>
       </c>
       <c r="C66">
-        <v>172.148581697298</v>
+        <v>152.2534219344558</v>
       </c>
       <c r="D66">
-        <v>531.508581697298</v>
+        <v>517.2284219344558</v>
       </c>
       <c r="E66">
-        <v>140.36</v>
+        <v>145.975</v>
       </c>
       <c r="F66">
-        <v>359.36</v>
+        <v>364.975</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6687,45 +6687,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M66">
-        <v>25.837984</v>
+        <v>27.665105</v>
       </c>
       <c r="N66">
-        <v>39.63701599999999</v>
+        <v>37.80989499999999</v>
       </c>
       <c r="O66">
-        <v>7.531033039999998</v>
+        <v>7.183880049999998</v>
       </c>
       <c r="P66">
-        <v>32.10598295999999</v>
+        <v>30.62601494999999</v>
       </c>
       <c r="Q66">
-        <v>44.50598295999999</v>
+        <v>43.02601494999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1279497209662105</v>
+        <v>0.1301140871509175</v>
       </c>
       <c r="T66">
-        <v>1.601250966826669</v>
+        <v>1.643438492299269</v>
       </c>
       <c r="U66">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V66">
         <v>0.19</v>
       </c>
       <c r="W66">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.534059932849249</v>
+        <v>2.366699855287012</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08544863050282112</v>
+        <v>0.08554064145780646</v>
       </c>
       <c r="C67">
-        <v>152.2534219344558</v>
+        <v>146.0342241011396</v>
       </c>
       <c r="D67">
-        <v>517.2284219344558</v>
+        <v>516.6242241011396</v>
       </c>
       <c r="E67">
-        <v>145.975</v>
+        <v>151.59</v>
       </c>
       <c r="F67">
-        <v>364.975</v>
+        <v>370.59</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6769,28 +6769,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M67">
-        <v>27.665105</v>
+        <v>28.090722</v>
       </c>
       <c r="N67">
-        <v>37.80989499999999</v>
+        <v>37.38427799999999</v>
       </c>
       <c r="O67">
-        <v>7.183880049999998</v>
+        <v>7.103012819999999</v>
       </c>
       <c r="P67">
-        <v>30.62601494999999</v>
+        <v>30.28126517999999</v>
       </c>
       <c r="Q67">
-        <v>43.02601494999999</v>
+        <v>42.68126518</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1301140871509175</v>
+        <v>0.1324057689935484</v>
       </c>
       <c r="T67">
-        <v>1.643438492299269</v>
+        <v>1.688107636917316</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.366699855287012</v>
+        <v>2.330840766570542</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08554064145780646</v>
+        <v>0.08563265241279178</v>
       </c>
       <c r="C68">
-        <v>146.0342241011396</v>
+        <v>139.8164362022611</v>
       </c>
       <c r="D68">
-        <v>516.6242241011396</v>
+        <v>516.0214362022612</v>
       </c>
       <c r="E68">
-        <v>151.59</v>
+        <v>157.205</v>
       </c>
       <c r="F68">
-        <v>370.59</v>
+        <v>376.205</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6851,28 +6851,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M68">
-        <v>28.090722</v>
+        <v>28.51633900000001</v>
       </c>
       <c r="N68">
-        <v>37.38427799999999</v>
+        <v>36.95866099999999</v>
       </c>
       <c r="O68">
-        <v>7.103012819999999</v>
+        <v>7.022145589999998</v>
       </c>
       <c r="P68">
-        <v>30.28126517999999</v>
+        <v>29.93651540999999</v>
       </c>
       <c r="Q68">
-        <v>42.68126518</v>
+        <v>42.33651540999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1324057689935484</v>
+        <v>0.1348363406448236</v>
       </c>
       <c r="T68">
-        <v>1.688107636917316</v>
+        <v>1.735484002421305</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.330840766570542</v>
+        <v>2.296052098412773</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08563265241279178</v>
+        <v>0.08572466336777711</v>
       </c>
       <c r="C69">
-        <v>139.8164362022611</v>
+        <v>133.6000533083131</v>
       </c>
       <c r="D69">
-        <v>516.0214362022612</v>
+        <v>515.4200533083132</v>
       </c>
       <c r="E69">
-        <v>157.205</v>
+        <v>162.8200000000001</v>
       </c>
       <c r="F69">
-        <v>376.205</v>
+        <v>381.8200000000001</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6933,28 +6933,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M69">
-        <v>28.51633900000001</v>
+        <v>28.941956</v>
       </c>
       <c r="N69">
-        <v>36.95866099999999</v>
+        <v>36.53304399999999</v>
       </c>
       <c r="O69">
-        <v>7.022145589999998</v>
+        <v>6.941278359999998</v>
       </c>
       <c r="P69">
-        <v>29.93651540999999</v>
+        <v>29.59176563999999</v>
       </c>
       <c r="Q69">
-        <v>42.33651540999999</v>
+        <v>41.99176563999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1348363406448236</v>
+        <v>0.1374188230243035</v>
       </c>
       <c r="T69">
-        <v>1.735484002421305</v>
+        <v>1.785821390769293</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.296052098412773</v>
+        <v>2.26228662637729</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08572466336777711</v>
+        <v>0.08581667432276244</v>
       </c>
       <c r="C70">
-        <v>133.6000533083131</v>
+        <v>127.3850705127417</v>
       </c>
       <c r="D70">
-        <v>515.4200533083132</v>
+        <v>514.8200705127417</v>
       </c>
       <c r="E70">
-        <v>162.8200000000001</v>
+        <v>168.4350000000001</v>
       </c>
       <c r="F70">
-        <v>381.8200000000001</v>
+        <v>387.4350000000001</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7015,28 +7015,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M70">
-        <v>28.941956</v>
+        <v>29.36757300000001</v>
       </c>
       <c r="N70">
-        <v>36.53304399999999</v>
+        <v>36.10742699999999</v>
       </c>
       <c r="O70">
-        <v>6.941278359999998</v>
+        <v>6.860411129999997</v>
       </c>
       <c r="P70">
-        <v>29.59176563999999</v>
+        <v>29.24701586999999</v>
       </c>
       <c r="Q70">
-        <v>41.99176563999999</v>
+        <v>41.64701586999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1374188230243035</v>
+        <v>0.1401679171702014</v>
       </c>
       <c r="T70">
-        <v>1.785821390769293</v>
+        <v>1.839406352559087</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.26228662637729</v>
+        <v>2.22949986367617</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08581667432276244</v>
+        <v>0.08590868527774777</v>
       </c>
       <c r="C71">
-        <v>127.3850705127417</v>
+        <v>121.1714829318122</v>
       </c>
       <c r="D71">
-        <v>514.8200705127417</v>
+        <v>514.2214829318123</v>
       </c>
       <c r="E71">
-        <v>168.4350000000001</v>
+        <v>174.05</v>
       </c>
       <c r="F71">
-        <v>387.4350000000001</v>
+        <v>393.05</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7097,28 +7097,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M71">
-        <v>29.36757300000001</v>
+        <v>29.79319</v>
       </c>
       <c r="N71">
-        <v>36.10742699999999</v>
+        <v>35.68180999999999</v>
       </c>
       <c r="O71">
-        <v>6.860411129999997</v>
+        <v>6.779543899999998</v>
       </c>
       <c r="P71">
-        <v>29.24701586999999</v>
+        <v>28.90226609999999</v>
       </c>
       <c r="Q71">
-        <v>41.64701586999999</v>
+        <v>41.30226609999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1401679171702014</v>
+        <v>0.1431002842591592</v>
       </c>
       <c r="T71">
-        <v>1.839406352559087</v>
+        <v>1.896563645134867</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.22949986367617</v>
+        <v>2.197649865623654</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08590868527774777</v>
+        <v>0.0860006962327331</v>
       </c>
       <c r="C72">
-        <v>121.1714829318122</v>
+        <v>114.9592857044775</v>
       </c>
       <c r="D72">
-        <v>514.2214829318123</v>
+        <v>513.6242857044775</v>
       </c>
       <c r="E72">
-        <v>174.05</v>
+        <v>179.665</v>
       </c>
       <c r="F72">
-        <v>393.05</v>
+        <v>398.665</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7179,28 +7179,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M72">
-        <v>29.79319</v>
+        <v>30.21880700000001</v>
       </c>
       <c r="N72">
-        <v>35.68180999999999</v>
+        <v>35.25619299999999</v>
       </c>
       <c r="O72">
-        <v>6.779543899999998</v>
+        <v>6.698676669999998</v>
       </c>
       <c r="P72">
-        <v>28.90226609999999</v>
+        <v>28.55751632999999</v>
       </c>
       <c r="Q72">
-        <v>41.30226609999999</v>
+        <v>40.95751632999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1431002842591592</v>
+        <v>0.1462348835611486</v>
       </c>
       <c r="T72">
-        <v>1.896563645134867</v>
+        <v>1.957662819957253</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.197649865623654</v>
+        <v>2.16669705061487</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0860006962327331</v>
+        <v>0.08609270718771841</v>
       </c>
       <c r="C73">
-        <v>114.9592857044776</v>
+        <v>108.748473992246</v>
       </c>
       <c r="D73">
-        <v>513.6242857044775</v>
+        <v>513.0284739922459</v>
       </c>
       <c r="E73">
-        <v>179.665</v>
+        <v>185.28</v>
       </c>
       <c r="F73">
-        <v>398.665</v>
+        <v>404.28</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7261,28 +7261,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M73">
-        <v>30.218807</v>
+        <v>30.644424</v>
       </c>
       <c r="N73">
-        <v>35.256193</v>
+        <v>34.83057599999999</v>
       </c>
       <c r="O73">
-        <v>6.698676669999999</v>
+        <v>6.617809439999998</v>
       </c>
       <c r="P73">
-        <v>28.55751633</v>
+        <v>28.21276656</v>
       </c>
       <c r="Q73">
-        <v>40.95751633</v>
+        <v>40.61276656</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1462348835611486</v>
+        <v>0.1495933828132801</v>
       </c>
       <c r="T73">
-        <v>1.957662819957252</v>
+        <v>2.023126221552665</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.166697050614871</v>
+        <v>2.136604036022997</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08609270718771841</v>
+        <v>0.08618471814270376</v>
       </c>
       <c r="C74">
-        <v>108.748473992246</v>
+        <v>102.5390429790504</v>
       </c>
       <c r="D74">
-        <v>513.0284739922459</v>
+        <v>512.4340429790503</v>
       </c>
       <c r="E74">
-        <v>185.28</v>
+        <v>190.895</v>
       </c>
       <c r="F74">
-        <v>404.28</v>
+        <v>409.895</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7343,28 +7343,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M74">
-        <v>30.644424</v>
+        <v>31.070041</v>
       </c>
       <c r="N74">
-        <v>34.83057599999999</v>
+        <v>34.40495899999999</v>
       </c>
       <c r="O74">
-        <v>6.617809439999998</v>
+        <v>6.536942209999999</v>
       </c>
       <c r="P74">
-        <v>28.21276656</v>
+        <v>27.86801678999999</v>
       </c>
       <c r="Q74">
-        <v>40.61276656</v>
+        <v>40.26801678999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1495933828132801</v>
+        <v>0.1532006597877917</v>
       </c>
       <c r="T74">
-        <v>2.023126221552665</v>
+        <v>2.093438764006998</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.136604036022997</v>
+        <v>2.107335487584326</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08618471814270376</v>
+        <v>0.08627672909768908</v>
       </c>
       <c r="C75">
-        <v>102.5390429790504</v>
+        <v>96.33098787111931</v>
       </c>
       <c r="D75">
-        <v>512.4340429790503</v>
+        <v>511.8409878711193</v>
       </c>
       <c r="E75">
-        <v>190.895</v>
+        <v>196.51</v>
       </c>
       <c r="F75">
-        <v>409.895</v>
+        <v>415.51</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7425,28 +7425,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M75">
-        <v>31.070041</v>
+        <v>31.495658</v>
       </c>
       <c r="N75">
-        <v>34.40495899999999</v>
+        <v>33.97934199999999</v>
       </c>
       <c r="O75">
-        <v>6.536942209999999</v>
+        <v>6.456074979999998</v>
       </c>
       <c r="P75">
-        <v>27.86801678999999</v>
+        <v>27.52326701999999</v>
       </c>
       <c r="Q75">
-        <v>40.26801678999999</v>
+        <v>39.92326701999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1532006597877917</v>
+        <v>0.1570854196064964</v>
       </c>
       <c r="T75">
-        <v>2.093438764006998</v>
+        <v>2.169159963573202</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.107335487584326</v>
+        <v>2.078857980995348</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08627672909768908</v>
+        <v>0.08636874005267442</v>
       </c>
       <c r="C76">
-        <v>96.33098787111931</v>
+        <v>90.12430389684687</v>
       </c>
       <c r="D76">
-        <v>511.8409878711193</v>
+        <v>511.2493038968469</v>
       </c>
       <c r="E76">
-        <v>196.51</v>
+        <v>202.125</v>
       </c>
       <c r="F76">
-        <v>415.51</v>
+        <v>421.125</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7507,28 +7507,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M76">
-        <v>31.495658</v>
+        <v>31.921275</v>
       </c>
       <c r="N76">
-        <v>33.97934199999999</v>
+        <v>33.55372499999999</v>
       </c>
       <c r="O76">
-        <v>6.456074979999998</v>
+        <v>6.375207749999999</v>
       </c>
       <c r="P76">
-        <v>27.52326701999999</v>
+        <v>27.17851725</v>
       </c>
       <c r="Q76">
-        <v>39.92326701999999</v>
+        <v>39.57851724999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1570854196064964</v>
+        <v>0.1612809602106976</v>
       </c>
       <c r="T76">
-        <v>2.169159963573202</v>
+        <v>2.250938859104703</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.078857980995348</v>
+        <v>2.051139874582077</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08636874005267442</v>
+        <v>0.08646075100765974</v>
       </c>
       <c r="C77">
-        <v>90.12430389684687</v>
+        <v>83.91898630666623</v>
       </c>
       <c r="D77">
-        <v>511.2493038968469</v>
+        <v>510.6589863066662</v>
       </c>
       <c r="E77">
-        <v>202.125</v>
+        <v>207.74</v>
       </c>
       <c r="F77">
-        <v>421.125</v>
+        <v>426.74</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7589,28 +7589,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M77">
-        <v>31.921275</v>
+        <v>32.346892</v>
       </c>
       <c r="N77">
-        <v>33.55372499999999</v>
+        <v>33.12810799999999</v>
       </c>
       <c r="O77">
-        <v>6.375207749999999</v>
+        <v>6.294340519999999</v>
       </c>
       <c r="P77">
-        <v>27.17851725</v>
+        <v>26.83376747999999</v>
       </c>
       <c r="Q77">
-        <v>39.57851724999999</v>
+        <v>39.23376747999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1612809602106976</v>
+        <v>0.1658261291985822</v>
       </c>
       <c r="T77">
-        <v>2.250938859104703</v>
+        <v>2.339532662597163</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.051139874582077</v>
+        <v>2.024151192021787</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08646075100765974</v>
+        <v>0.09540930196264506</v>
       </c>
       <c r="C78">
-        <v>83.91898630666623</v>
+        <v>26.74829852836791</v>
       </c>
       <c r="D78">
-        <v>510.6589863066662</v>
+        <v>459.1032985283679</v>
       </c>
       <c r="E78">
-        <v>207.74</v>
+        <v>213.355</v>
       </c>
       <c r="F78">
-        <v>426.74</v>
+        <v>432.355</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7671,45 +7671,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M78">
-        <v>32.346892</v>
+        <v>38.91195</v>
       </c>
       <c r="N78">
-        <v>33.12810799999999</v>
+        <v>26.56305</v>
       </c>
       <c r="O78">
-        <v>6.294340519999999</v>
+        <v>5.046979499999999</v>
       </c>
       <c r="P78">
-        <v>26.83376747999999</v>
+        <v>21.5160705</v>
       </c>
       <c r="Q78">
-        <v>39.23376747999999</v>
+        <v>33.9160705</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1658261291985822</v>
+        <v>0.1707665302723698</v>
       </c>
       <c r="T78">
-        <v>2.339532662597163</v>
+        <v>2.435830275088966</v>
       </c>
       <c r="U78">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V78">
         <v>0.19</v>
       </c>
       <c r="W78">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.024151192021787</v>
+        <v>1.68264504862902</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09540930196264506</v>
+        <v>0.09561633291763039</v>
       </c>
       <c r="C79">
-        <v>26.74829852836791</v>
+        <v>20.06344243510108</v>
       </c>
       <c r="D79">
-        <v>459.1032985283679</v>
+        <v>458.0334424351011</v>
       </c>
       <c r="E79">
-        <v>213.355</v>
+        <v>218.97</v>
       </c>
       <c r="F79">
-        <v>432.355</v>
+        <v>437.97</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7753,28 +7753,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M79">
-        <v>38.91195</v>
+        <v>39.4173</v>
       </c>
       <c r="N79">
-        <v>26.56305</v>
+        <v>26.05769999999999</v>
       </c>
       <c r="O79">
-        <v>5.046979499999999</v>
+        <v>4.950962999999998</v>
       </c>
       <c r="P79">
-        <v>21.5160705</v>
+        <v>21.10673699999999</v>
       </c>
       <c r="Q79">
-        <v>33.9160705</v>
+        <v>33.50673699999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1707665302723698</v>
+        <v>0.1761560587165018</v>
       </c>
       <c r="T79">
-        <v>2.435830275088966</v>
+        <v>2.540882215989115</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.68264504862902</v>
+        <v>1.661072676210699</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09561633291763039</v>
+        <v>0.09582336387261572</v>
       </c>
       <c r="C80">
-        <v>20.06344243510108</v>
+        <v>13.38356095649306</v>
       </c>
       <c r="D80">
-        <v>458.0334424351011</v>
+        <v>456.9685609564931</v>
       </c>
       <c r="E80">
-        <v>218.97</v>
+        <v>224.585</v>
       </c>
       <c r="F80">
-        <v>437.97</v>
+        <v>443.585</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7835,28 +7835,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M80">
-        <v>39.4173</v>
+        <v>39.92265</v>
       </c>
       <c r="N80">
-        <v>26.05769999999999</v>
+        <v>25.55234999999999</v>
       </c>
       <c r="O80">
-        <v>4.950962999999998</v>
+        <v>4.854946499999998</v>
       </c>
       <c r="P80">
-        <v>21.10673699999999</v>
+        <v>20.69740349999999</v>
       </c>
       <c r="Q80">
-        <v>33.50673699999999</v>
+        <v>33.09740349999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1761560587165018</v>
+        <v>0.1820588755838844</v>
       </c>
       <c r="T80">
-        <v>2.540882215989115</v>
+        <v>2.65593910364166</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.661072676210699</v>
+        <v>1.640046439802969</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09582336387261572</v>
+        <v>0.09603039482760106</v>
       </c>
       <c r="C81">
-        <v>13.38356095649306</v>
+        <v>6.708619476592958</v>
       </c>
       <c r="D81">
-        <v>456.9685609564931</v>
+        <v>455.908619476593</v>
       </c>
       <c r="E81">
-        <v>224.585</v>
+        <v>230.2</v>
       </c>
       <c r="F81">
-        <v>443.585</v>
+        <v>449.2</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7917,28 +7917,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M81">
-        <v>39.92265</v>
+        <v>40.428</v>
       </c>
       <c r="N81">
-        <v>25.55234999999999</v>
+        <v>25.04699999999999</v>
       </c>
       <c r="O81">
-        <v>4.854946499999998</v>
+        <v>4.758929999999999</v>
       </c>
       <c r="P81">
-        <v>20.69740349999999</v>
+        <v>20.28806999999999</v>
       </c>
       <c r="Q81">
-        <v>33.09740349999999</v>
+        <v>32.68806999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1820588755838844</v>
+        <v>0.1885519741380053</v>
       </c>
       <c r="T81">
-        <v>2.65593910364166</v>
+        <v>2.782501680059459</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.640046439802969</v>
+        <v>1.619545859305432</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09603039482760106</v>
+        <v>0.09623742578258637</v>
       </c>
       <c r="C82">
-        <v>6.708619476592958</v>
+        <v>0.0385836998744935</v>
       </c>
       <c r="D82">
-        <v>455.908619476593</v>
+        <v>454.8535836998745</v>
       </c>
       <c r="E82">
-        <v>230.2</v>
+        <v>235.8150000000001</v>
       </c>
       <c r="F82">
-        <v>449.2</v>
+        <v>454.8150000000001</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7999,28 +7999,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M82">
-        <v>40.428</v>
+        <v>40.93335</v>
       </c>
       <c r="N82">
-        <v>25.04699999999999</v>
+        <v>24.54164999999999</v>
       </c>
       <c r="O82">
-        <v>4.758929999999999</v>
+        <v>4.662913499999998</v>
       </c>
       <c r="P82">
-        <v>20.28806999999999</v>
+        <v>19.87873649999999</v>
       </c>
       <c r="Q82">
-        <v>32.68806999999999</v>
+        <v>32.27873649999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1885519741380053</v>
+        <v>0.1957285567504546</v>
       </c>
       <c r="T82">
-        <v>2.782501680059459</v>
+        <v>2.92238663294229</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.619545859305432</v>
+        <v>1.599551465980673</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09623742578258637</v>
+        <v>0.09644445673757171</v>
       </c>
       <c r="C83">
-        <v>0.0385836998744935</v>
+        <v>-6.626580352463463</v>
       </c>
       <c r="D83">
-        <v>454.8535836998745</v>
+        <v>453.8034196475365</v>
       </c>
       <c r="E83">
-        <v>235.8150000000001</v>
+        <v>241.43</v>
       </c>
       <c r="F83">
-        <v>454.8150000000001</v>
+        <v>460.43</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8081,28 +8081,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M83">
-        <v>40.93335</v>
+        <v>41.4387</v>
       </c>
       <c r="N83">
-        <v>24.54164999999999</v>
+        <v>24.0363</v>
       </c>
       <c r="O83">
-        <v>4.662913499999998</v>
+        <v>4.566896999999999</v>
       </c>
       <c r="P83">
-        <v>19.87873649999999</v>
+        <v>19.469403</v>
       </c>
       <c r="Q83">
-        <v>32.27873649999999</v>
+        <v>31.869403</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1957285567504546</v>
+        <v>0.2037025374309539</v>
       </c>
       <c r="T83">
-        <v>2.92238663294229</v>
+        <v>3.077814358367656</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.599551465980673</v>
+        <v>1.580044740785787</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09644445673757171</v>
+        <v>0.09665148769255703</v>
       </c>
       <c r="C84">
-        <v>-6.626580352463463</v>
+        <v>-13.28690634614429</v>
       </c>
       <c r="D84">
-        <v>453.8034196475365</v>
+        <v>452.7580936538557</v>
       </c>
       <c r="E84">
-        <v>241.43</v>
+        <v>247.045</v>
       </c>
       <c r="F84">
-        <v>460.43</v>
+        <v>466.045</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8163,28 +8163,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M84">
-        <v>41.4387</v>
+        <v>41.94405</v>
       </c>
       <c r="N84">
-        <v>24.0363</v>
+        <v>23.53095</v>
       </c>
       <c r="O84">
-        <v>4.566896999999999</v>
+        <v>4.4708805</v>
       </c>
       <c r="P84">
-        <v>19.469403</v>
+        <v>19.0600695</v>
       </c>
       <c r="Q84">
-        <v>31.869403</v>
+        <v>31.4600695</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2037025374309539</v>
+        <v>0.2126146334856296</v>
       </c>
       <c r="T84">
-        <v>3.077814358367656</v>
+        <v>3.251527698548949</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.580044740785787</v>
+        <v>1.561008057161862</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09665148769255703</v>
+        <v>0.09685851864754236</v>
       </c>
       <c r="C85">
-        <v>-13.28690634614429</v>
+        <v>-19.94242763741124</v>
       </c>
       <c r="D85">
-        <v>452.7580936538557</v>
+        <v>451.7175723625888</v>
       </c>
       <c r="E85">
-        <v>247.045</v>
+        <v>252.66</v>
       </c>
       <c r="F85">
-        <v>466.045</v>
+        <v>471.66</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8245,28 +8245,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M85">
-        <v>41.94405</v>
+        <v>42.4494</v>
       </c>
       <c r="N85">
-        <v>23.53095</v>
+        <v>23.0256</v>
       </c>
       <c r="O85">
-        <v>4.4708805</v>
+        <v>4.374864</v>
       </c>
       <c r="P85">
-        <v>19.0600695</v>
+        <v>18.650736</v>
       </c>
       <c r="Q85">
-        <v>31.4600695</v>
+        <v>31.050736</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2126146334856296</v>
+        <v>0.2226407415471398</v>
       </c>
       <c r="T85">
-        <v>3.251527698548949</v>
+        <v>3.446955206252904</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.561008057161862</v>
+        <v>1.542424627909935</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09685851864754236</v>
+        <v>0.0970655496025277</v>
       </c>
       <c r="C86">
-        <v>-19.94242763741119</v>
+        <v>-26.5931772765756</v>
       </c>
       <c r="D86">
-        <v>451.7175723625888</v>
+        <v>450.6818227234244</v>
       </c>
       <c r="E86">
-        <v>252.66</v>
+        <v>258.275</v>
       </c>
       <c r="F86">
-        <v>471.66</v>
+        <v>477.275</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8327,28 +8327,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M86">
-        <v>42.4494</v>
+        <v>42.95475</v>
       </c>
       <c r="N86">
-        <v>23.0256</v>
+        <v>22.52025</v>
       </c>
       <c r="O86">
-        <v>4.374864</v>
+        <v>4.278847499999999</v>
       </c>
       <c r="P86">
-        <v>18.650736</v>
+        <v>18.2414025</v>
       </c>
       <c r="Q86">
-        <v>31.050736</v>
+        <v>30.6414025</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2226407415471397</v>
+        <v>0.2340036640168512</v>
       </c>
       <c r="T86">
-        <v>3.446955206252901</v>
+        <v>3.66843971498405</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.542424627909935</v>
+        <v>1.524278455816877</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0970655496025277</v>
+        <v>0.09727258055751301</v>
       </c>
       <c r="C87">
-        <v>-26.5931772765756</v>
+        <v>-33.23918801151586</v>
       </c>
       <c r="D87">
-        <v>450.6818227234244</v>
+        <v>449.6508119884841</v>
       </c>
       <c r="E87">
-        <v>258.275</v>
+        <v>263.89</v>
       </c>
       <c r="F87">
-        <v>477.275</v>
+        <v>482.89</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8409,28 +8409,28 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M87">
-        <v>42.95475</v>
+        <v>43.4601</v>
       </c>
       <c r="N87">
-        <v>22.52025</v>
+        <v>22.0149</v>
       </c>
       <c r="O87">
-        <v>4.278847499999999</v>
+        <v>4.182830999999999</v>
       </c>
       <c r="P87">
-        <v>18.2414025</v>
+        <v>17.832069</v>
       </c>
       <c r="Q87">
-        <v>30.6414025</v>
+        <v>30.232069</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2340036640168512</v>
+        <v>0.2469898611250929</v>
       </c>
       <c r="T87">
-        <v>3.66843971498405</v>
+        <v>3.921564867819648</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.524278455816877</v>
+        <v>1.506554287725983</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09727258055751301</v>
+        <v>0.1401012928293615</v>
       </c>
       <c r="C88">
-        <v>-33.23918801151586</v>
+        <v>-183.2953869502649</v>
       </c>
       <c r="D88">
-        <v>449.6508119884841</v>
+        <v>305.2096130497351</v>
       </c>
       <c r="E88">
-        <v>263.89</v>
+        <v>269.505</v>
       </c>
       <c r="F88">
-        <v>482.89</v>
+        <v>488.505</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8491,45 +8491,45 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M88">
-        <v>43.4601</v>
+        <v>71.71253400000001</v>
       </c>
       <c r="N88">
-        <v>22.0149</v>
+        <v>-6.237534000000011</v>
       </c>
       <c r="O88">
-        <v>4.182830999999999</v>
+        <v>-1.185131460000002</v>
       </c>
       <c r="P88">
-        <v>17.832069</v>
+        <v>-5.052402540000009</v>
       </c>
       <c r="Q88">
-        <v>30.232069</v>
+        <v>7.34759745999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2469898611250929</v>
+        <v>0.265697539881998</v>
       </c>
       <c r="T88">
-        <v>3.921564867819648</v>
+        <v>4.286212347375886</v>
       </c>
       <c r="U88">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.19</v>
+        <v>0.1734738588375639</v>
       </c>
       <c r="W88">
-        <v>0.07290000000000001</v>
+        <v>0.1213340375226456</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>1.506554287725983</v>
+        <v>0.9130203096713887</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1401012928293615</v>
+        <v>0.1411112928293614</v>
       </c>
       <c r="C89">
-        <v>-183.2953869502649</v>
+        <v>-191.2050701645027</v>
       </c>
       <c r="D89">
-        <v>305.2096130497351</v>
+        <v>302.9149298354973</v>
       </c>
       <c r="E89">
-        <v>269.505</v>
+        <v>275.12</v>
       </c>
       <c r="F89">
-        <v>488.505</v>
+        <v>494.12</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8573,37 +8573,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M89">
-        <v>71.71253400000001</v>
+        <v>72.536816</v>
       </c>
       <c r="N89">
-        <v>-6.237534000000011</v>
+        <v>-7.061816000000007</v>
       </c>
       <c r="O89">
-        <v>-1.185131460000002</v>
+        <v>-1.341745040000001</v>
       </c>
       <c r="P89">
-        <v>-5.052402540000009</v>
+        <v>-5.720070960000006</v>
       </c>
       <c r="Q89">
-        <v>7.34759745999999</v>
+        <v>6.679929039999992</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.265697539881998</v>
+        <v>0.2840223348721646</v>
       </c>
       <c r="T89">
-        <v>4.286212347375886</v>
+        <v>4.643396709657211</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1734738588375639</v>
+        <v>0.171502564987137</v>
       </c>
       <c r="W89">
-        <v>0.1213340375226456</v>
+        <v>0.1216234234598883</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9130203096713887</v>
+        <v>0.9026450788796684</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1411112928293614</v>
+        <v>0.1421212928293615</v>
       </c>
       <c r="C90">
-        <v>-191.2050701645027</v>
+        <v>-199.080506240618</v>
       </c>
       <c r="D90">
-        <v>302.9149298354973</v>
+        <v>300.654493759382</v>
       </c>
       <c r="E90">
-        <v>275.12</v>
+        <v>280.735</v>
       </c>
       <c r="F90">
-        <v>494.12</v>
+        <v>499.735</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8655,37 +8655,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M90">
-        <v>72.536816</v>
+        <v>73.36109800000001</v>
       </c>
       <c r="N90">
-        <v>-7.061816000000007</v>
+        <v>-7.886098000000018</v>
       </c>
       <c r="O90">
-        <v>-1.341745040000001</v>
+        <v>-1.498358620000003</v>
       </c>
       <c r="P90">
-        <v>-5.720070960000006</v>
+        <v>-6.387739380000015</v>
       </c>
       <c r="Q90">
-        <v>6.679929039999992</v>
+        <v>6.012260619999983</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2840223348721646</v>
+        <v>0.305678910769634</v>
       </c>
       <c r="T90">
-        <v>4.643396709657211</v>
+        <v>5.065523683262413</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.171502564987137</v>
+        <v>0.1695755698749219</v>
       </c>
       <c r="W90">
-        <v>0.1216234234598883</v>
+        <v>0.1219063063423615</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9026450788796684</v>
+        <v>0.8925029993416944</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1421212928293615</v>
+        <v>0.1431312928293615</v>
       </c>
       <c r="C91">
-        <v>-199.080506240618</v>
+        <v>-206.9224561849878</v>
       </c>
       <c r="D91">
-        <v>300.654493759382</v>
+        <v>298.4275438150123</v>
       </c>
       <c r="E91">
-        <v>280.735</v>
+        <v>286.35</v>
       </c>
       <c r="F91">
-        <v>499.735</v>
+        <v>505.35</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8737,37 +8737,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M91">
-        <v>73.36109800000001</v>
+        <v>74.18538000000001</v>
       </c>
       <c r="N91">
-        <v>-7.886098000000018</v>
+        <v>-8.710380000000015</v>
       </c>
       <c r="O91">
-        <v>-1.498358620000003</v>
+        <v>-1.654972200000003</v>
       </c>
       <c r="P91">
-        <v>-6.387739380000015</v>
+        <v>-7.055407800000012</v>
       </c>
       <c r="Q91">
-        <v>6.012260619999983</v>
+        <v>5.344592199999987</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.305678910769634</v>
+        <v>0.3316668018465975</v>
       </c>
       <c r="T91">
-        <v>5.065523683262413</v>
+        <v>5.572076051588654</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1695755698749219</v>
+        <v>0.1676913968763117</v>
       </c>
       <c r="W91">
-        <v>0.1219063063423615</v>
+        <v>0.1221829029385574</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8925029993416944</v>
+        <v>0.882586299349009</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1431312928293615</v>
+        <v>0.1441412928293614</v>
       </c>
       <c r="C92">
-        <v>-206.9224561849878</v>
+        <v>-214.7316586226494</v>
       </c>
       <c r="D92">
-        <v>298.4275438150123</v>
+        <v>296.2333413773507</v>
       </c>
       <c r="E92">
-        <v>286.35</v>
+        <v>291.965</v>
       </c>
       <c r="F92">
-        <v>505.35</v>
+        <v>510.965</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8819,37 +8819,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M92">
-        <v>74.18538000000001</v>
+        <v>75.00966200000001</v>
       </c>
       <c r="N92">
-        <v>-8.710380000000015</v>
+        <v>-9.534662000000012</v>
       </c>
       <c r="O92">
-        <v>-1.654972200000003</v>
+        <v>-1.811585780000002</v>
       </c>
       <c r="P92">
-        <v>-7.055407800000012</v>
+        <v>-7.723076220000009</v>
       </c>
       <c r="Q92">
-        <v>5.344592199999987</v>
+        <v>4.676923779999989</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3316668018465975</v>
+        <v>0.3634297798295528</v>
       </c>
       <c r="T92">
-        <v>5.572076051588654</v>
+        <v>6.191195612876283</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1676913968763117</v>
+        <v>0.1658486342732753</v>
       </c>
       <c r="W92">
-        <v>0.1221829029385574</v>
+        <v>0.1224534204886832</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.882586299349009</v>
+        <v>0.8728875488067123</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1441412928293614</v>
+        <v>0.1451512928293615</v>
       </c>
       <c r="C93">
-        <v>-214.7316586226494</v>
+        <v>-222.5088306140945</v>
       </c>
       <c r="D93">
-        <v>296.2333413773507</v>
+        <v>294.0711693859055</v>
       </c>
       <c r="E93">
-        <v>291.965</v>
+        <v>297.58</v>
       </c>
       <c r="F93">
-        <v>510.965</v>
+        <v>516.58</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8901,37 +8901,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M93">
-        <v>75.00966200000001</v>
+        <v>75.83394400000002</v>
       </c>
       <c r="N93">
-        <v>-9.534662000000012</v>
+        <v>-10.35894400000002</v>
       </c>
       <c r="O93">
-        <v>-1.811585780000002</v>
+        <v>-1.968199360000004</v>
       </c>
       <c r="P93">
-        <v>-7.723076220000009</v>
+        <v>-8.390744640000019</v>
       </c>
       <c r="Q93">
-        <v>4.676923779999989</v>
+        <v>4.00925535999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3634297798295528</v>
+        <v>0.403133502308247</v>
       </c>
       <c r="T93">
-        <v>6.191195612876283</v>
+        <v>6.96509506448582</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1658486342732753</v>
+        <v>0.1640459317268267</v>
       </c>
       <c r="W93">
-        <v>0.1224534204886832</v>
+        <v>0.1227180572225019</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8728875488067123</v>
+        <v>0.8633996406675087</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1451512928293615</v>
+        <v>0.1461612928293614</v>
       </c>
       <c r="C94">
-        <v>-222.5088306140945</v>
+        <v>-230.2546684365514</v>
       </c>
       <c r="D94">
-        <v>294.0711693859055</v>
+        <v>291.9403315634486</v>
       </c>
       <c r="E94">
-        <v>297.58</v>
+        <v>303.1950000000001</v>
       </c>
       <c r="F94">
-        <v>516.58</v>
+        <v>522.1950000000001</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8983,37 +8983,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M94">
-        <v>75.83394400000002</v>
+        <v>76.65822600000001</v>
       </c>
       <c r="N94">
-        <v>-10.35894400000002</v>
+        <v>-11.18322600000002</v>
       </c>
       <c r="O94">
-        <v>-1.968199360000004</v>
+        <v>-2.124812940000004</v>
       </c>
       <c r="P94">
-        <v>-8.390744640000019</v>
+        <v>-9.058413060000015</v>
       </c>
       <c r="Q94">
-        <v>4.00925535999998</v>
+        <v>3.341586939999983</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.403133502308247</v>
+        <v>0.4541811454951394</v>
       </c>
       <c r="T94">
-        <v>6.96509506448582</v>
+        <v>7.960108645126653</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1640459317268267</v>
+        <v>0.1622819969770758</v>
       </c>
       <c r="W94">
-        <v>0.1227180572225019</v>
+        <v>0.1229770028437653</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8633996406675087</v>
+        <v>0.8541157735635571</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1461612928293614</v>
+        <v>0.1471712928293614</v>
       </c>
       <c r="C95">
-        <v>-230.2546684365514</v>
+        <v>-237.9698483315459</v>
       </c>
       <c r="D95">
-        <v>291.9403315634486</v>
+        <v>289.8401516684542</v>
       </c>
       <c r="E95">
-        <v>303.1950000000001</v>
+        <v>308.8100000000001</v>
       </c>
       <c r="F95">
-        <v>522.1950000000001</v>
+        <v>527.8100000000001</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9065,37 +9065,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M95">
-        <v>76.65822600000001</v>
+        <v>77.48250800000001</v>
       </c>
       <c r="N95">
-        <v>-11.18322600000002</v>
+        <v>-12.00750800000002</v>
       </c>
       <c r="O95">
-        <v>-2.124812940000004</v>
+        <v>-2.281426520000003</v>
       </c>
       <c r="P95">
-        <v>-9.058413060000015</v>
+        <v>-9.726081480000012</v>
       </c>
       <c r="Q95">
-        <v>3.341586939999983</v>
+        <v>2.673918519999987</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4541811454951394</v>
+        <v>0.5222446697443294</v>
       </c>
       <c r="T95">
-        <v>7.960108645126653</v>
+        <v>9.28679341931443</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1622819969770758</v>
+        <v>0.1605555927539155</v>
       </c>
       <c r="W95">
-        <v>0.1229770028437653</v>
+        <v>0.1232304389837252</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8541157735635571</v>
+        <v>0.8450294355469236</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1471712928293614</v>
+        <v>0.1481812928293615</v>
       </c>
       <c r="C96">
-        <v>-237.9698483315459</v>
+        <v>-245.6550272204243</v>
       </c>
       <c r="D96">
-        <v>289.8401516684542</v>
+        <v>287.7699727795758</v>
       </c>
       <c r="E96">
-        <v>308.8100000000001</v>
+        <v>314.4250000000001</v>
       </c>
       <c r="F96">
-        <v>527.8100000000001</v>
+        <v>533.4250000000001</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9147,37 +9147,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M96">
-        <v>77.48250800000001</v>
+        <v>78.30679000000002</v>
       </c>
       <c r="N96">
-        <v>-12.00750800000002</v>
+        <v>-12.83179000000003</v>
       </c>
       <c r="O96">
-        <v>-2.281426520000003</v>
+        <v>-2.438040100000005</v>
       </c>
       <c r="P96">
-        <v>-9.726081480000012</v>
+        <v>-10.39374990000002</v>
       </c>
       <c r="Q96">
-        <v>2.673918519999987</v>
+        <v>2.006250099999978</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5222446697443294</v>
+        <v>0.6175336036931958</v>
       </c>
       <c r="T96">
-        <v>9.28679341931443</v>
+        <v>11.14415210317732</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1605555927539155</v>
+        <v>0.1588655338828216</v>
       </c>
       <c r="W96">
-        <v>0.1232304389837252</v>
+        <v>0.1234785396260018</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8450294355469236</v>
+        <v>0.8361343888569558</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1481812928293615</v>
+        <v>0.1491912928293614</v>
       </c>
       <c r="C97">
-        <v>-245.6550272204243</v>
+        <v>-253.3108433894305</v>
       </c>
       <c r="D97">
-        <v>287.7699727795758</v>
+        <v>285.7291566105695</v>
       </c>
       <c r="E97">
-        <v>314.4250000000001</v>
+        <v>320.0400000000001</v>
       </c>
       <c r="F97">
-        <v>533.4250000000001</v>
+        <v>539.0400000000001</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9229,37 +9229,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M97">
-        <v>78.30679000000002</v>
+        <v>79.13107200000002</v>
       </c>
       <c r="N97">
-        <v>-12.83179000000003</v>
+        <v>-13.65607200000002</v>
       </c>
       <c r="O97">
-        <v>-2.438040100000005</v>
+        <v>-2.594653680000004</v>
       </c>
       <c r="P97">
-        <v>-10.39374990000002</v>
+        <v>-11.06141832000002</v>
       </c>
       <c r="Q97">
-        <v>2.006250099999978</v>
+        <v>1.338581679999979</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6175336036931958</v>
+        <v>0.7604670046164949</v>
       </c>
       <c r="T97">
-        <v>11.14415210317732</v>
+        <v>13.93019012897166</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1588655338828216</v>
+        <v>0.1572106845715422</v>
       </c>
       <c r="W97">
-        <v>0.1234785396260018</v>
+        <v>0.1237214715048976</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8361343888569558</v>
+        <v>0.8274246556396958</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1491912928293614</v>
+        <v>0.1502012928293614</v>
       </c>
       <c r="C98">
-        <v>-253.3108433894304</v>
+        <v>-260.9379171458385</v>
       </c>
       <c r="D98">
-        <v>285.7291566105695</v>
+        <v>283.7170828541614</v>
       </c>
       <c r="E98">
-        <v>320.04</v>
+        <v>325.655</v>
       </c>
       <c r="F98">
-        <v>539.04</v>
+        <v>544.655</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9311,37 +9311,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M98">
-        <v>79.131072</v>
+        <v>79.955354</v>
       </c>
       <c r="N98">
-        <v>-13.65607200000001</v>
+        <v>-14.48035400000001</v>
       </c>
       <c r="O98">
-        <v>-2.594653680000002</v>
+        <v>-2.751267260000001</v>
       </c>
       <c r="P98">
-        <v>-11.06141832000001</v>
+        <v>-11.72908674</v>
       </c>
       <c r="Q98">
-        <v>1.338581679999992</v>
+        <v>0.6709132599999936</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.760467004616493</v>
+        <v>0.9986893394886572</v>
       </c>
       <c r="T98">
-        <v>13.93019012897162</v>
+        <v>18.57358683862883</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1572106845715422</v>
+        <v>0.1555899558646192</v>
       </c>
       <c r="W98">
-        <v>0.1237214715048976</v>
+        <v>0.1239593944790739</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.827424655639696</v>
+        <v>0.8188945045506271</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1502012928293614</v>
+        <v>0.1512112928293615</v>
       </c>
       <c r="C99">
-        <v>-260.9379171458385</v>
+        <v>-268.5368514465555</v>
       </c>
       <c r="D99">
-        <v>283.7170828541614</v>
+        <v>281.7331485534445</v>
       </c>
       <c r="E99">
-        <v>325.655</v>
+        <v>331.27</v>
       </c>
       <c r="F99">
-        <v>544.655</v>
+        <v>550.27</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9393,37 +9393,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M99">
-        <v>79.955354</v>
+        <v>80.77963600000001</v>
       </c>
       <c r="N99">
-        <v>-14.48035400000001</v>
+        <v>-15.30463600000002</v>
       </c>
       <c r="O99">
-        <v>-2.751267260000001</v>
+        <v>-2.907880840000003</v>
       </c>
       <c r="P99">
-        <v>-11.72908674</v>
+        <v>-12.39675516000001</v>
       </c>
       <c r="Q99">
-        <v>0.6709132599999936</v>
+        <v>0.003244839999986482</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9986893394886572</v>
+        <v>1.475134009232986</v>
       </c>
       <c r="T99">
-        <v>18.57358683862883</v>
+        <v>27.86038025794324</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1555899558646192</v>
+        <v>0.1540023032537557</v>
       </c>
       <c r="W99">
-        <v>0.1239593944790739</v>
+        <v>0.1241924618823487</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8188945045506271</v>
+        <v>0.8105384381776614</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1512112928293615</v>
+        <v>0.1522212928293614</v>
       </c>
       <c r="C100">
-        <v>-268.5368514465555</v>
+        <v>-276.1082325005338</v>
       </c>
       <c r="D100">
-        <v>281.7331485534445</v>
+        <v>279.7767674994662</v>
       </c>
       <c r="E100">
-        <v>331.27</v>
+        <v>336.885</v>
       </c>
       <c r="F100">
-        <v>550.27</v>
+        <v>555.885</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9475,37 +9475,37 @@
         <v>65.47499999999999</v>
       </c>
       <c r="M100">
-        <v>80.77963600000001</v>
+        <v>81.60391800000001</v>
       </c>
       <c r="N100">
-        <v>-15.30463600000002</v>
+        <v>-16.12891800000001</v>
       </c>
       <c r="O100">
-        <v>-2.907880840000003</v>
+        <v>-3.064494420000003</v>
       </c>
       <c r="P100">
-        <v>-12.39675516000001</v>
+        <v>-13.06442358000001</v>
       </c>
       <c r="Q100">
-        <v>0.003244839999986482</v>
+        <v>-0.6644235800000118</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.475134009232986</v>
+        <v>2.904468018465972</v>
       </c>
       <c r="T100">
-        <v>27.86038025794324</v>
+        <v>55.72076051588649</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1540023032537557</v>
+        <v>0.1524467244330107</v>
       </c>
       <c r="W100">
-        <v>0.1241924618823487</v>
+        <v>0.124420820853234</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8105384381776614</v>
+        <v>0.8023511812263718</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1522212928293614</v>
-      </c>
-      <c r="C101">
-        <v>-276.1082325005338</v>
-      </c>
-      <c r="D101">
-        <v>279.7767674994662</v>
-      </c>
-      <c r="E101">
-        <v>336.885</v>
-      </c>
-      <c r="F101">
-        <v>555.885</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>342.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>77.87499999999999</v>
-      </c>
-      <c r="K101">
-        <v>12.4</v>
-      </c>
-      <c r="L101">
-        <v>65.47499999999999</v>
-      </c>
-      <c r="M101">
-        <v>81.60391800000001</v>
-      </c>
-      <c r="N101">
-        <v>-16.12891800000001</v>
-      </c>
-      <c r="O101">
-        <v>-3.064494420000003</v>
-      </c>
-      <c r="P101">
-        <v>-13.06442358000001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.6644235800000118</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.904468018465972</v>
-      </c>
-      <c r="T101">
-        <v>55.72076051588649</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1524467244330107</v>
-      </c>
-      <c r="W101">
-        <v>0.124420820853234</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8023511812263718</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
